--- a/offers_output.xlsx
+++ b/offers_output.xlsx
@@ -182,16 +182,16 @@
     <t>Body (iç giyim)</t>
   </si>
   <si>
-    <t>1.199,00 TL - 1.182,01 TL</t>
-  </si>
-  <si>
-    <t>8 %</t>
+    <t>1.208,00 TL - 1.182,01 TL</t>
+  </si>
+  <si>
+    <t>7,1 %</t>
   </si>
   <si>
     <t>1.182,00 TL - 1.143,01 TL</t>
   </si>
   <si>
-    <t>7,1 %</t>
+    <t>6,4 %</t>
   </si>
   <si>
     <t>1.143,00 TL - ve altı</t>
@@ -203,43 +203,88 @@
     <t>18,00 %</t>
   </si>
   <si>
+    <t>Dagi Erkek Termal Tek Alt Siyah E010910890</t>
+  </si>
+  <si>
+    <t>HBV000007F6MK</t>
+  </si>
+  <si>
+    <t>HB000008HS9N</t>
+  </si>
+  <si>
+    <t>1.088,00 TL - 1.049,01 TL</t>
+  </si>
+  <si>
+    <t>1.049,00 TL - 1.013,01 TL</t>
+  </si>
+  <si>
+    <t>1.013,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>5 %</t>
+  </si>
+  <si>
+    <t>Dagi Termal Tek Alt Esnek Kumaşla Rahatlık Sağlayan Erkek İç Giyim</t>
+  </si>
+  <si>
+    <t>HBV000002OBQA</t>
+  </si>
+  <si>
+    <t>1.103,00 TL - 1.064,01 TL</t>
+  </si>
+  <si>
+    <t>1.064,00 TL - 1.027,01 TL</t>
+  </si>
+  <si>
+    <t>1.027,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>HBV000007F6ML</t>
+  </si>
+  <si>
     <t>Dagi Erkek Termal Tek Alt İçlik XL Siyah Renk Esnek Kumaşla Şıklığı Yakalayın</t>
   </si>
   <si>
     <t>HBV000003GUOS</t>
   </si>
   <si>
-    <t>HB000008HS9N</t>
-  </si>
-  <si>
-    <t>8,5 %</t>
-  </si>
-  <si>
-    <t>7,8 %</t>
-  </si>
-  <si>
-    <t>6,4 %</t>
-  </si>
-  <si>
-    <t>Dagi Erkek Termal Tek Alt Siyah E010910890</t>
-  </si>
-  <si>
-    <t>HBV000007F6MK</t>
-  </si>
-  <si>
-    <t>1.169,00 TL - 1.143,01 TL</t>
-  </si>
-  <si>
-    <t>1.143,00 TL - 1.130,01 TL</t>
-  </si>
-  <si>
-    <t>1.130,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>Erdem İç Giyim Erdem Beyaz Amerikan Yaka T-Shirt 3XL Erkekler İçin Yumuşak Dokulu Nefes Alabilir Kumaş 1165</t>
-  </si>
-  <si>
-    <t>HBV000018HGPQ</t>
+    <t>Erdem 3'lü 1110 Ribana Erkek Atlet</t>
+  </si>
+  <si>
+    <t>HBV00000A54QC</t>
+  </si>
+  <si>
+    <t>HB00000A54Q5</t>
+  </si>
+  <si>
+    <t>Atlet</t>
+  </si>
+  <si>
+    <t>805,00 TL - 788,01 TL</t>
+  </si>
+  <si>
+    <t>788,00 TL - 754,01 TL</t>
+  </si>
+  <si>
+    <t>754,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>HBV00000A54QM</t>
+  </si>
+  <si>
+    <t>791,00 TL - 774,01 TL</t>
+  </si>
+  <si>
+    <t>774,00 TL - 742,01 TL</t>
+  </si>
+  <si>
+    <t>742,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Erdem İç Giyim Erdem Beyaz Penye Amerikan Yaka T-Shirt Erkekler İçin Yumuşak Dokulu 100% Pamuklu</t>
+  </si>
+  <si>
+    <t>HBV000018HGPM</t>
   </si>
   <si>
     <t>HB000018HGPK</t>
@@ -248,205 +293,295 @@
     <t>Fanila</t>
   </si>
   <si>
-    <t>539,00 TL - 501,01 TL</t>
-  </si>
-  <si>
-    <t>501,00 TL - 486,01 TL</t>
-  </si>
-  <si>
-    <t>486,00 TL - ve altı</t>
+    <t>507,00 TL - 489,01 TL</t>
+  </si>
+  <si>
+    <t>489,00 TL - 474,01 TL</t>
+  </si>
+  <si>
+    <t>474,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Erdem İç Giyim Beyaz Amerikan Yaka T-Shirt Erkek S Beden Yumuşak Dokulu Pamuklu Kumaş</t>
+  </si>
+  <si>
+    <t>HBV000018HGPL</t>
   </si>
   <si>
     <t>Erdem Beyaz Penye Amerikan Yaka T-Shirt 1165</t>
   </si>
   <si>
-    <t>HBV000018HGPP</t>
-  </si>
-  <si>
-    <t>556,00 TL - 501,01 TL</t>
-  </si>
-  <si>
-    <t>3'lü Erdem 1440 Poplın Erkek Boxer</t>
-  </si>
-  <si>
-    <t>HBCV000001LF73</t>
-  </si>
-  <si>
-    <t>HBC000001LF71</t>
-  </si>
-  <si>
-    <t>Boxer</t>
-  </si>
-  <si>
-    <t>642,00 TL - 621,01 TL</t>
+    <t>HBV000018HGPN</t>
+  </si>
+  <si>
+    <t>Erdem İç Giyim Erdem Beyaz Penye Amerikan Yaka T-Shirt Erkek XL Konforlu Yazlık İç Giyim</t>
+  </si>
+  <si>
+    <t>HBV000018HGPO</t>
+  </si>
+  <si>
+    <t>505,00 TL - 479,01 TL</t>
+  </si>
+  <si>
+    <t>479,00 TL - 455,01 TL</t>
+  </si>
+  <si>
+    <t>455,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Dagi Kadın Sütyen B0169255SY</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7N</t>
+  </si>
+  <si>
+    <t>HBC000021TR4M</t>
+  </si>
+  <si>
+    <t>Hamile İç Giyim</t>
+  </si>
+  <si>
+    <t>576,00 TL - 547,01 TL</t>
   </si>
   <si>
     <t>6,8 %</t>
   </si>
   <si>
-    <t>621,00 TL - 607,01 TL</t>
+    <t>547,00 TL - 519,01 TL</t>
   </si>
   <si>
     <t>5,9 %</t>
   </si>
   <si>
-    <t>607,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>5 %</t>
-  </si>
-  <si>
-    <t>HBCV000001LF74</t>
-  </si>
-  <si>
-    <t>HBCV000001LF72</t>
+    <t>519,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7O</t>
+  </si>
+  <si>
+    <t>652,00 TL - 631,01 TL</t>
+  </si>
+  <si>
+    <t>631,00 TL - 610,01 TL</t>
+  </si>
+  <si>
+    <t>6,3 %</t>
+  </si>
+  <si>
+    <t>610,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>5,2 %</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7M</t>
+  </si>
+  <si>
+    <t>5,3 %</t>
+  </si>
+  <si>
+    <t>Dagi Kadın Sütyen B0169255TE</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7T</t>
+  </si>
+  <si>
+    <t>HBC000021TR4Z</t>
+  </si>
+  <si>
+    <t>577,00 TL - 548,01 TL</t>
+  </si>
+  <si>
+    <t>6,6 %</t>
+  </si>
+  <si>
+    <t>548,00 TL - 520,01 TL</t>
+  </si>
+  <si>
+    <t>5,8 %</t>
+  </si>
+  <si>
+    <t>520,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7R</t>
+  </si>
+  <si>
+    <t>601,00 TL - 581,01 TL</t>
+  </si>
+  <si>
+    <t>7,5 %</t>
+  </si>
+  <si>
+    <t>581,00 TL - 561,01 TL</t>
+  </si>
+  <si>
+    <t>6,7 %</t>
+  </si>
+  <si>
+    <t>561,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>5,6 %</t>
+  </si>
+  <si>
+    <t>Dagi Kadın Lohusa Atlet Beyaz</t>
+  </si>
+  <si>
+    <t>HBV00000BPKBZ</t>
+  </si>
+  <si>
+    <t>HBC000021TR5B</t>
+  </si>
+  <si>
+    <t>516,00 TL - 498,01 TL</t>
+  </si>
+  <si>
+    <t>7,2 %</t>
+  </si>
+  <si>
+    <t>498,00 TL - 481,01 TL</t>
+  </si>
+  <si>
+    <t>6,5 %</t>
+  </si>
+  <si>
+    <t>481,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>5,1 %</t>
+  </si>
+  <si>
+    <t>Dagi Beyaz Emzirme Atleti Kadınlar İçin Yumuşak ve Nefes Alabilir Pamuk Elastan Karışımı</t>
+  </si>
+  <si>
+    <t>HBV00000BPKBY</t>
+  </si>
+  <si>
+    <t>523,00 TL - 506,01 TL</t>
+  </si>
+  <si>
+    <t>506,00 TL - 489,01 TL</t>
+  </si>
+  <si>
+    <t>489,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>5,4 %</t>
+  </si>
+  <si>
+    <t>Dagi Kadın Lohusa Atlet Siyah</t>
+  </si>
+  <si>
+    <t>HBV00000BPKCB</t>
+  </si>
+  <si>
+    <t>HBC000021TR5L</t>
+  </si>
+  <si>
+    <t>490,00 TL - 474,01 TL</t>
+  </si>
+  <si>
+    <t>7,4 %</t>
+  </si>
+  <si>
+    <t>474,00 TL - 458,01 TL</t>
+  </si>
+  <si>
+    <t>458,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Dagi Siyah Lohusa Emzirme Atleti Kadın İç Giyim %95 Pamuk Esnek Kumaş Özellikli</t>
+  </si>
+  <si>
+    <t>HBV00000BPKCA</t>
+  </si>
+  <si>
+    <t>499,00 TL - 482,01 TL</t>
+  </si>
+  <si>
+    <t>10,1 %</t>
+  </si>
+  <si>
+    <t>482,00 TL - 465,01 TL</t>
+  </si>
+  <si>
+    <t>6,2 %</t>
+  </si>
+  <si>
+    <t>465,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Dagi Kadın 2'Li Atlet Beyaz</t>
+  </si>
+  <si>
+    <t>HBV00000BPJHW</t>
+  </si>
+  <si>
+    <t>HBC000021TW6H</t>
+  </si>
+  <si>
+    <t>678,00 TL - 656,01 TL</t>
+  </si>
+  <si>
+    <t>7,3 %</t>
+  </si>
+  <si>
+    <t>656,00 TL - 635,01 TL</t>
+  </si>
+  <si>
+    <t>635,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>5,5 %</t>
+  </si>
+  <si>
+    <t>Beyaz 2'Li İnce Askılı Penye Kadın Atlet</t>
+  </si>
+  <si>
+    <t>HBV00000BPJHV</t>
+  </si>
+  <si>
+    <t>HBV00000BPJHU</t>
+  </si>
+  <si>
+    <t>HBV00000BPJHZ</t>
   </si>
   <si>
     <t>6,9 %</t>
   </si>
   <si>
-    <t>6 %</t>
-  </si>
-  <si>
-    <t>Dagi Kadın Sütyen B0169255SY</t>
-  </si>
-  <si>
-    <t>HBV00000AKT7M</t>
-  </si>
-  <si>
-    <t>HBC000021TR4M</t>
-  </si>
-  <si>
-    <t>Hamile İç Giyim</t>
-  </si>
-  <si>
-    <t>836,00 TL - 809,01 TL</t>
-  </si>
-  <si>
-    <t>809,00 TL - 800,01 TL</t>
-  </si>
-  <si>
-    <t>800,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>HBV00000AKT7O</t>
-  </si>
-  <si>
-    <t>HBV00000AKT7N</t>
-  </si>
-  <si>
-    <t>604,00 TL - 584,01 TL</t>
-  </si>
-  <si>
-    <t>6,7 %</t>
-  </si>
-  <si>
-    <t>584,00 TL - 577,01 TL</t>
-  </si>
-  <si>
-    <t>6,2 %</t>
-  </si>
-  <si>
-    <t>577,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>5,1 %</t>
-  </si>
-  <si>
-    <t>Dagi Kadın Sütyen B0169255TE</t>
-  </si>
-  <si>
-    <t>HBV00000AKT7T</t>
-  </si>
-  <si>
-    <t>HBC000021TR4Z</t>
-  </si>
-  <si>
-    <t>Dagi Kadın Lohusa Atlet Beyaz</t>
-  </si>
-  <si>
-    <t>HBV00000BPKBZ</t>
-  </si>
-  <si>
-    <t>HBC000021TR5B</t>
-  </si>
-  <si>
-    <t>Atlet</t>
-  </si>
-  <si>
-    <t>8,3 %</t>
-  </si>
-  <si>
-    <t>584,00 TL - 571,01 TL</t>
-  </si>
-  <si>
-    <t>7,3 %</t>
-  </si>
-  <si>
-    <t>571,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>Dagi Beyaz Emzirme Atleti Kadınlar İçin Yumuşak ve Nefes Alabilir Pamuk Elastan Karışımı</t>
-  </si>
-  <si>
-    <t>HBV00000BPKBY</t>
-  </si>
-  <si>
-    <t>8,2 %</t>
-  </si>
-  <si>
-    <t>7,4 %</t>
-  </si>
-  <si>
-    <t>Dagi Siyah Lohusa Emzirme Atleti Kadın İç Giyim %95 Pamuk Esnek Kumaş Özellikli</t>
-  </si>
-  <si>
-    <t>HBV00000BPKCA</t>
-  </si>
-  <si>
-    <t>HBC000021TR5L</t>
-  </si>
-  <si>
-    <t>8,1 %</t>
-  </si>
-  <si>
-    <t>5,8 %</t>
-  </si>
-  <si>
-    <t>Dagi Kadın 2'Li Atlet Beyaz</t>
-  </si>
-  <si>
-    <t>HBV00000BPJHU</t>
-  </si>
-  <si>
-    <t>HBC000021TW6H</t>
-  </si>
-  <si>
-    <t>929,00 TL - 899,01 TL</t>
-  </si>
-  <si>
-    <t>899,00 TL - 879,01 TL</t>
-  </si>
-  <si>
-    <t>879,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>HBV00000BPJHZ</t>
-  </si>
-  <si>
-    <t>HBV00000BPJHW</t>
-  </si>
-  <si>
-    <t>Beyaz 2'Li İnce Askılı Penye Kadın Atlet</t>
-  </si>
-  <si>
-    <t>HBV00000BPJHV</t>
+    <t>6,1 %</t>
+  </si>
+  <si>
+    <t>HBV00000BPJHX</t>
+  </si>
+  <si>
+    <t>716,00 TL - 692,01 TL</t>
+  </si>
+  <si>
+    <t>692,00 TL - 669,01 TL</t>
+  </si>
+  <si>
+    <t>669,00 TL - ve altı</t>
   </si>
   <si>
     <t>HBV00000BPJHY</t>
   </si>
   <si>
-    <t>HBV00000BPJHX</t>
+    <t>Dagi Kadın 2'Li Siyah Atlet Rahat Kesim Pamuk %95 Elastan Nefes Alabilir</t>
+  </si>
+  <si>
+    <t>HBV00000BPJI4</t>
+  </si>
+  <si>
+    <t>HBC000021TX1L</t>
+  </si>
+  <si>
+    <t>677,00 TL - 655,01 TL</t>
+  </si>
+  <si>
+    <t>655,00 TL - 635,01 TL</t>
   </si>
   <si>
     <t>Siyah 2'Li İnce Askılı Penye Kadın Atlet</t>
@@ -455,13 +590,22 @@
     <t>HBV00000BPJI2</t>
   </si>
   <si>
-    <t>HBC000021TX1L</t>
-  </si>
-  <si>
-    <t>Dagi Kadın 2'Li Siyah Atlet Rahat Kesim Pamuk %95 Elastan Nefes Alabilir</t>
-  </si>
-  <si>
-    <t>HBV00000BPJI4</t>
+    <t>Dagi Kadın 2'Li Siyah Atlet %95 Pamuk %5 Elastan Nefes Alabilir Rahat Kesim</t>
+  </si>
+  <si>
+    <t>HBV00000BPJI3</t>
+  </si>
+  <si>
+    <t>Dagi Siyah Kadın Atlet 2'li İnce Askılı Esnek Kumaş Özelliği ile Pamuk ve Elastan Karışımı</t>
+  </si>
+  <si>
+    <t>HBV00000BPJI6</t>
+  </si>
+  <si>
+    <t>Dagi Kadın 2'Li Siyah Atlet %95 Pamuk Elastik Yapı ile Gün Boyu Rahatlık Sunar</t>
+  </si>
+  <si>
+    <t>HBV00000BPJI5</t>
   </si>
   <si>
     <t>Dagi Kadın Siyah 2'Li Atlet %95 Pamuk Esnek Kumaş Özelliği ile Rahat Kullanım</t>
@@ -470,22 +614,31 @@
     <t>HBV00000BPJI1</t>
   </si>
   <si>
-    <t>Dagi Kadın 2'Li Siyah Atlet %95 Pamuk %5 Elastan Nefes Alabilir Rahat Kesim</t>
-  </si>
-  <si>
-    <t>HBV00000BPJI3</t>
-  </si>
-  <si>
-    <t>Dagi Siyah Kadın Atlet 2'li İnce Askılı Esnek Kumaş Özelliği ile Pamuk ve Elastan Karışımı</t>
-  </si>
-  <si>
-    <t>HBV00000BPJI6</t>
-  </si>
-  <si>
-    <t>Dagi Kadın 2'Li Siyah Atlet %95 Pamuk Elastik Yapı ile Gün Boyu Rahatlık Sunar</t>
-  </si>
-  <si>
-    <t>HBV00000BPJI5</t>
+    <t>674,00 TL - 653,01 TL</t>
+  </si>
+  <si>
+    <t>653,00 TL - 632,01 TL</t>
+  </si>
+  <si>
+    <t>632,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Dagi Kadın Sütyen 95B Beyaz Konforlu Tasarım Yumuşak Dokulu Pamuk ve Elastan Kumaş</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7I</t>
+  </si>
+  <si>
+    <t>HBC000021TYSW</t>
+  </si>
+  <si>
+    <t>646,00 TL - 624,01 TL</t>
+  </si>
+  <si>
+    <t>624,00 TL - 603,01 TL</t>
+  </si>
+  <si>
+    <t>603,00 TL - ve altı</t>
   </si>
   <si>
     <t>Dagi Emzirme Sütyeni – Yumuşak Dokulu, Esnek Yapılı, %95 Pamuk %5 Elastan, Düz Desenli, Rahat Emzirme İçin</t>
@@ -494,22 +647,19 @@
     <t>HBV00000AKT7E</t>
   </si>
   <si>
-    <t>HBC000021TYSW</t>
-  </si>
-  <si>
-    <t>Dagi Kadın Sütyen 95B Beyaz Konforlu Tasarım Yumuşak Dokulu Pamuk ve Elastan Kumaş</t>
-  </si>
-  <si>
-    <t>HBV00000AKT7I</t>
-  </si>
-  <si>
-    <t>811,00 TL - 785,01 TL</t>
-  </si>
-  <si>
-    <t>785,00 TL - 776,01 TL</t>
-  </si>
-  <si>
-    <t>776,00 TL - ve altı</t>
+    <t>538,00 TL - 511,01 TL</t>
+  </si>
+  <si>
+    <t>511,00 TL - 485,01 TL</t>
+  </si>
+  <si>
+    <t>485,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Dagi Kadın Sütyen Yumuşak Dokulu Beyaz %95 Pamuk %5 Elastan Konforlu Tasarım ile B0169255BY</t>
+  </si>
+  <si>
+    <t>HBV00000AKT7G</t>
   </si>
   <si>
     <t>Dagi Kadın Sütyen B0169255BY %95 Pamuk %5 Elastan Yumuşak Dokulu Konforlu Tasarım</t>
@@ -518,22 +668,37 @@
     <t>HBV00000AKT7H</t>
   </si>
   <si>
-    <t>6,6 %</t>
-  </si>
-  <si>
-    <t>6,1 %</t>
-  </si>
-  <si>
-    <t>Dagi Kadın Sütyen Yumuşak Dokulu Beyaz %95 Pamuk %5 Elastan Konforlu Tasarım ile B0169255BY</t>
-  </si>
-  <si>
-    <t>HBV00000AKT7G</t>
-  </si>
-  <si>
-    <t>6,3 %</t>
-  </si>
-  <si>
-    <t>5,2 %</t>
+    <t>Dagi Erkek Termal Tek Alt Ekru Yumuşak Doku ve Esnek Kumaş ile Konforlu Kullanım E010910890</t>
+  </si>
+  <si>
+    <t>HBV000007F6MB</t>
+  </si>
+  <si>
+    <t>HBC000021U1V4</t>
+  </si>
+  <si>
+    <t>Dagi Erkek Termal İçlik Tek Alt Ekru Renk Esnek Kumaş ile Gün Boyu Rahatlık 2XL</t>
+  </si>
+  <si>
+    <t>HBV000008HS9P</t>
+  </si>
+  <si>
+    <t>Dagi Erkek Termal Tek Alt Ekru</t>
+  </si>
+  <si>
+    <t>HBV000008HS9O</t>
+  </si>
+  <si>
+    <t>Dagi Erkek Termal Tek Alt Siyah</t>
+  </si>
+  <si>
+    <t>HBCV0000A7T9AE</t>
+  </si>
+  <si>
+    <t>Dagi Erkek Termal Tek Alt Ekru E010910890</t>
+  </si>
+  <si>
+    <t>HBV000007F6MA</t>
   </si>
   <si>
     <t>Dagi Termal Tek Alt E010910890Ek</t>
@@ -542,37 +707,16 @@
     <t>HBV000002OBQ6</t>
   </si>
   <si>
-    <t>HBC000021U1V4</t>
-  </si>
-  <si>
-    <t>Dagi Erkek Termal Tek Alt Ekru</t>
-  </si>
-  <si>
-    <t>HBV000008HS9O</t>
-  </si>
-  <si>
-    <t>Dagi Erkek Termal Tek Alt Ekru Yumuşak Doku ve Esnek Kumaş ile Konforlu Kullanım E010910890</t>
-  </si>
-  <si>
-    <t>HBV000007F6MB</t>
-  </si>
-  <si>
-    <t>Dagi Erkek Termal İçlik Tek Alt Ekru Renk Esnek Kumaş ile Gün Boyu Rahatlık 2XL</t>
-  </si>
-  <si>
-    <t>HBV000008HS9P</t>
-  </si>
-  <si>
-    <t>Dagi Erkek Termal Tek Alt Ekru E010910890</t>
-  </si>
-  <si>
-    <t>HBV000007F6MA</t>
-  </si>
-  <si>
-    <t>Dagi Erkek Termal Tek Alt Siyah</t>
-  </si>
-  <si>
-    <t>HBCV0000A7T9AE</t>
+    <t>935,00 TL - 904,01 TL</t>
+  </si>
+  <si>
+    <t>904,00 TL - 875,01 TL</t>
+  </si>
+  <si>
+    <t>875,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>HBCV0000A7T9AF</t>
   </si>
   <si>
     <t>Dagi Siyah Termal Erkek Atlet</t>
@@ -584,7 +728,7 @@
     <t>HBC000021U233</t>
   </si>
   <si>
-    <t>849,00 TL - 845,01 TL</t>
+    <t>863,00 TL - 845,01 TL</t>
   </si>
   <si>
     <t>845,00 TL - 809,01 TL</t>
@@ -599,10 +743,31 @@
     <t>HBCV000002FS92</t>
   </si>
   <si>
-    <t>809,00 TL - 791,01 TL</t>
-  </si>
-  <si>
-    <t>791,00 TL - ve altı</t>
+    <t>617,00 TL - 597,01 TL</t>
+  </si>
+  <si>
+    <t>597,00 TL - 578,01 TL</t>
+  </si>
+  <si>
+    <t>578,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Siyah V Yaka Uzun Kol Erkek Termal Içlik Tek Üst</t>
+  </si>
+  <si>
+    <t>HBCV0000AAZFB1</t>
+  </si>
+  <si>
+    <t>HBC000021U2XK</t>
+  </si>
+  <si>
+    <t>957,00 TL - 941,01 TL</t>
+  </si>
+  <si>
+    <t>941,00 TL - 929,01 TL</t>
+  </si>
+  <si>
+    <t>929,00 TL - ve altı</t>
   </si>
   <si>
     <t>Siyah V Yaka Uzun Kol Erkek Termal İçlik Tek Üst</t>
@@ -611,16 +776,31 @@
     <t>HBV000007F6PG</t>
   </si>
   <si>
-    <t>HBC000021U2XK</t>
-  </si>
-  <si>
-    <t>1.034,00 TL - 1.011,01 TL</t>
-  </si>
-  <si>
-    <t>1.011,00 TL - 1.000,01 TL</t>
-  </si>
-  <si>
-    <t>1.000,00 TL - ve altı</t>
+    <t>832,00 TL - 804,01 TL</t>
+  </si>
+  <si>
+    <t>804,00 TL - 778,01 TL</t>
+  </si>
+  <si>
+    <t>778,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Fabony Modal Hamile Boxer Şort 1110</t>
+  </si>
+  <si>
+    <t>HBCV00003AXTEB</t>
+  </si>
+  <si>
+    <t>HBC00003AXSS8</t>
+  </si>
+  <si>
+    <t>312,00 TL - 311,01 TL</t>
+  </si>
+  <si>
+    <t>311,00 TL - 307,01 TL</t>
+  </si>
+  <si>
+    <t>307,00 TL - ve altı</t>
   </si>
   <si>
     <t>Ten Iz Yapmaz Ultra Ince Silikon Sütyen</t>
@@ -635,61 +815,61 @@
     <t>Sütyen</t>
   </si>
   <si>
-    <t>318,00 TL - 315,01 TL</t>
-  </si>
-  <si>
-    <t>315,00 TL - 304,01 TL</t>
-  </si>
-  <si>
-    <t>304,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>Dagi V Yaka Kısa Kol Erkek Termal Içlik</t>
-  </si>
-  <si>
-    <t>HBCV0000CG46YK</t>
-  </si>
-  <si>
-    <t>HBC0000CG46YJ</t>
-  </si>
-  <si>
-    <t>Dagi V Yaka Kısa Kol Erkek Termal Içlik %47 Polyester %47 Viskoz Siyah Renkli Yumuşak Kumaş</t>
-  </si>
-  <si>
-    <t>HBCV0000CG4DQ1</t>
-  </si>
-  <si>
-    <t>Dagi Kısa Kol Erkek Termal İçlik V Yaka 2XL %47 Polyester %47 Viskoz Yumuşak ve Rahat Kumaş</t>
-  </si>
-  <si>
-    <t>HBCV0000CG46P8</t>
+    <t>322,00 TL - 318,01 TL</t>
+  </si>
+  <si>
+    <t>318,00 TL - 310,01 TL</t>
+  </si>
+  <si>
+    <t>310,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t>Dagi Ten Renkli Yapışkansız Silikon Göğüs Ucu Kapatıcı Gün Boyu Destek ve Konforlu Tasarım</t>
+  </si>
+  <si>
+    <t>HBCV000094IRFH</t>
+  </si>
+  <si>
+    <t>HBC000094IRFG</t>
+  </si>
+  <si>
+    <t>112,00 TL - 110,01 TL</t>
+  </si>
+  <si>
+    <t>7,7 %</t>
+  </si>
+  <si>
+    <t>110,00 TL - 97,01 TL</t>
+  </si>
+  <si>
+    <t>97,00 TL - ve altı</t>
   </si>
   <si>
     <t>Pierre Cardin 4560 Madrid Balenli Dolgusuz Dantel Detaylı Sütyen Takımı (Pudra)</t>
   </si>
   <si>
+    <t>HBCV0000DH6BOM</t>
+  </si>
+  <si>
+    <t>HBC0000DH69S2</t>
+  </si>
+  <si>
+    <t>783,00 TL - 766,01 TL</t>
+  </si>
+  <si>
+    <t>766,00 TL - 679,01 TL</t>
+  </si>
+  <si>
+    <t>679,00 TL - ve altı</t>
+  </si>
+  <si>
     <t>HBCV0000DH6AUH</t>
   </si>
   <si>
-    <t>HBC0000DH69S2</t>
-  </si>
-  <si>
-    <t>775,00 TL - 766,01 TL</t>
-  </si>
-  <si>
-    <t>766,00 TL - 679,01 TL</t>
-  </si>
-  <si>
-    <t>679,00 TL - ve altı</t>
-  </si>
-  <si>
-    <t>HBCV0000DH6BOM</t>
-  </si>
-  <si>
-    <t>766,00 TL - 743,01 TL</t>
-  </si>
-  <si>
-    <t>743,00 TL - 679,01 TL</t>
+    <t>809,00 TL - 783,01 TL</t>
+  </si>
+  <si>
+    <t>766,00 TL - ve altı</t>
   </si>
   <si>
     <t>Pierre Cardin 4563 Pisa Balenli Dolgulu Push Up Dantel Straplez Fantezi Sütyen ve Külot Takımı</t>
@@ -701,13 +881,13 @@
     <t>HBC0000DH69SE</t>
   </si>
   <si>
-    <t>809,00 TL - 783,01 TL</t>
-  </si>
-  <si>
-    <t>783,00 TL - 766,01 TL</t>
-  </si>
-  <si>
-    <t>766,00 TL - ve altı</t>
+    <t>564,00 TL - 546,01 TL</t>
+  </si>
+  <si>
+    <t>546,00 TL - 530,01 TL</t>
+  </si>
+  <si>
+    <t>530,00 TL - ve altı</t>
   </si>
   <si>
     <t>Kadınlar İçin Pierre Cardin 6020 Bej Renk Straplez Balenli Sütyen Gün Boyu Destek Sağlayan Tasarım</t>
@@ -719,13 +899,40 @@
     <t>HBC0000DH6AOB</t>
   </si>
   <si>
-    <t>586,00 TL - 567,01 TL</t>
-  </si>
-  <si>
-    <t>567,00 TL - 554,01 TL</t>
-  </si>
-  <si>
-    <t>554,00 TL - ve altı</t>
+    <t>507,00 TL - 481,01 TL</t>
+  </si>
+  <si>
+    <t>481,00 TL - 456,01 TL</t>
+  </si>
+  <si>
+    <t>456,00 TL - ve altı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre Cardin  6020 Straplez Sütyen Beyaz Renk B Beden ile Gün Boyu Destek Sağlar</t>
+  </si>
+  <si>
+    <t>HBCV0000DH6BOO</t>
+  </si>
+  <si>
+    <t>Pierre Cardin 6020 Balenli Kadın Sütyen Bej Renk Straplez Desteksiz 80B Gün Boyu Destek</t>
+  </si>
+  <si>
+    <t>HBCV0000DH6AOC</t>
+  </si>
+  <si>
+    <t>Pierre Cardin 6020 Balenli Straplez Sütyen Bej 90B Desteksiz Gün Boyu Destek Sunan</t>
+  </si>
+  <si>
+    <t>HBCV0000DH6CAA</t>
+  </si>
+  <si>
+    <t>427,00 TL - 413,01 TL</t>
+  </si>
+  <si>
+    <t>413,00 TL - 400,01 TL</t>
+  </si>
+  <si>
+    <t>400,00 TL - ve altı</t>
   </si>
   <si>
     <t>Pierre Cardin 6020 Balenli Kadın Sütyen Bej Renk 85B Straplez Desteksiz Gün Boyu Destek</t>
@@ -734,40 +941,19 @@
     <t>HBCV0000DH6AOL</t>
   </si>
   <si>
-    <t>Pierre Cardin 6020 Balenli Straplez Tek Sütyen Beyaz Renk B Kap Kadınlar İçin Desteksiz Tasarım</t>
-  </si>
-  <si>
-    <t>HBCV0000DH6B0S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pierre Cardin Balenli  6020 Straplez Kadın Sütyen Beyaz Renk B Beden Gün Boyu Destek Sağlar</t>
-  </si>
-  <si>
-    <t>HBCV0000DH6BBD</t>
+    <t>433,00 TL - 419,01 TL</t>
+  </si>
+  <si>
+    <t>419,00 TL - 405,01 TL</t>
+  </si>
+  <si>
+    <t>405,00 TL - ve altı</t>
   </si>
   <si>
     <t>Pierre Cardin 6020 Balenli Straplez Tek Sütyen 75B Beyaz Renk Desteksiz Konforlu Tasarım</t>
   </si>
   <si>
     <t>HBCV0000DH6BOW</t>
-  </si>
-  <si>
-    <t>Pierre Cardin 6020 Balenli Straplez Sütyen Bej 90B Desteksiz Gün Boyu Destek Sunan</t>
-  </si>
-  <si>
-    <t>HBCV0000DH6CAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pierre Cardin  6020 Straplez Sütyen Beyaz Renk B Beden ile Gün Boyu Destek Sağlar</t>
-  </si>
-  <si>
-    <t>HBCV0000DH6BOO</t>
-  </si>
-  <si>
-    <t>Pierre Cardin 6020 Balenli Kadın Sütyen Bej Renk Straplez Desteksiz 80B Gün Boyu Destek</t>
-  </si>
-  <si>
-    <t>HBCV0000DH6AOC</t>
   </si>
 </sst>
 </file>
@@ -7722,7 +7908,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="33">
-        <v>135538414</v>
+        <v>135940778</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>48</v>
@@ -7737,13 +7923,13 @@
         <v>51</v>
       </c>
       <c r="F2" s="34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="35">
-        <v>46120.052402407397</v>
+        <v>46127.146887766197</v>
       </c>
       <c r="H2" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I2" s="36" t="s">
         <v>52</v>
@@ -7752,7 +7938,7 @@
         <v>53</v>
       </c>
       <c r="K2" s="38">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="L2" s="39" t="s">
         <v>54</v>
@@ -7779,11 +7965,11 @@
         <v>58</v>
       </c>
       <c r="T2" s="34" t="str">
-        <f>IF(ISBLANK(U2),SUBSTITUTE("18 %",".",","),IF(U2&lt;=1143,SUBSTITUTE("5.7 %",".",","),IF(U2&lt;=1182,SUBSTITUTE("7.1 %",".",","),IF(U2&lt;=1199,SUBSTITUTE("8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8 %</v>
+        <f>IF(ISBLANK(U2),SUBSTITUTE("18 %",".",","),IF(U2&lt;=1143,SUBSTITUTE("5.7 %",".",","),IF(U2&lt;=1182,SUBSTITUTE("6.4 %",".",","),IF(U2&lt;=1208,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>7,1 %</v>
       </c>
       <c r="U2" s="46">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="V2"/>
       <c r="W2"/>
@@ -7801,7 +7987,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="33">
-        <v>135559579</v>
+        <v>135842540</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>59</v>
@@ -7816,40 +8002,40 @@
         <v>51</v>
       </c>
       <c r="F3" s="34">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G3" s="35">
-        <v>46120.05552021991</v>
+        <v>46127.129810856481</v>
       </c>
       <c r="H3" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I3" s="36" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K3" s="38">
-        <v>1199</v>
+        <v>1088</v>
       </c>
       <c r="L3" s="39" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="M3" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N3" s="41">
-        <v>1182</v>
+        <v>1049</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q3" s="43">
-        <v>1143</v>
+        <v>1013</v>
       </c>
       <c r="R3" s="44">
         <v>1299</v>
@@ -7858,11 +8044,11 @@
         <v>58</v>
       </c>
       <c r="T3" s="34" t="str">
-        <f>IF(ISBLANK(U3),SUBSTITUTE("18 %",".",","),IF(U3&lt;=1143,SUBSTITUTE("6.4 %",".",","),IF(U3&lt;=1182,SUBSTITUTE("7.8 %",".",","),IF(U3&lt;=1199,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U3),SUBSTITUTE("18 %",".",","),IF(U3&lt;=1013,SUBSTITUTE("5 %",".",","),IF(U3&lt;=1049,SUBSTITUTE("5.7 %",".",","),IF(U3&lt;=1088,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U3" s="46">
-        <v>1199</v>
+        <v>1088</v>
       </c>
       <c r="V3"/>
       <c r="W3"/>
@@ -7880,13 +8066,13 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="33">
-        <v>135559228</v>
+        <v>135838126</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>61</v>
@@ -7895,40 +8081,40 @@
         <v>51</v>
       </c>
       <c r="F4" s="34">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G4" s="35">
-        <v>46120.055471388892</v>
+        <v>46127.128773124998</v>
       </c>
       <c r="H4" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K4" s="38">
-        <v>1169</v>
+        <v>1103</v>
       </c>
       <c r="L4" s="39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M4" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N4" s="41">
-        <v>1143</v>
+        <v>1064</v>
       </c>
       <c r="O4" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q4" s="43">
-        <v>1130</v>
+        <v>1027</v>
       </c>
       <c r="R4" s="44">
         <v>1299</v>
@@ -7937,11 +8123,11 @@
         <v>58</v>
       </c>
       <c r="T4" s="34" t="str">
-        <f>IF(ISBLANK(U4),SUBSTITUTE("18 %",".",","),IF(U4&lt;=1130,SUBSTITUTE("6.4 %",".",","),IF(U4&lt;=1143,SUBSTITUTE("7.8 %",".",","),IF(U4&lt;=1169,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U4),SUBSTITUTE("18 %",".",","),IF(U4&lt;=1027,SUBSTITUTE("5 %",".",","),IF(U4&lt;=1064,SUBSTITUTE("5.7 %",".",","),IF(U4&lt;=1103,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U4" s="46">
-        <v>1169</v>
+        <v>1103</v>
       </c>
       <c r="V4"/>
       <c r="W4"/>
@@ -7959,68 +8145,68 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="33">
-        <v>135550326</v>
+        <v>135837552</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C5" s="34" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F5" s="34">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G5" s="35">
-        <v>46120.054093298611</v>
+        <v>46127.12863983796</v>
       </c>
       <c r="H5" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K5" s="38">
-        <v>539</v>
+        <v>1088</v>
       </c>
       <c r="L5" s="39" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="M5" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N5" s="41">
-        <v>501</v>
+        <v>1049</v>
       </c>
       <c r="O5" s="42" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="43">
-        <v>486</v>
+        <v>1013</v>
       </c>
       <c r="R5" s="44">
-        <v>649</v>
+        <v>1299</v>
       </c>
       <c r="S5" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T5" s="34" t="str">
-        <f>IF(ISBLANK(U5),SUBSTITUTE("18 %",".",","),IF(U5&lt;=486,SUBSTITUTE("6.4 %",".",","),IF(U5&lt;=501,SUBSTITUTE("7.8 %",".",","),IF(U5&lt;=539,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U5),SUBSTITUTE("18 %",".",","),IF(U5&lt;=1013,SUBSTITUTE("5 %",".",","),IF(U5&lt;=1049,SUBSTITUTE("5.7 %",".",","),IF(U5&lt;=1088,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U5" s="46">
-        <v>539</v>
+        <v>1088</v>
       </c>
       <c r="V5"/>
       <c r="W5"/>
@@ -8038,68 +8224,68 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="33">
-        <v>135515461</v>
+        <v>135819827</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F6" s="34">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G6" s="35">
-        <v>46120.046380277781</v>
+        <v>46127.125264988434</v>
       </c>
       <c r="H6" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K6" s="38">
-        <v>556</v>
+        <v>1103</v>
       </c>
       <c r="L6" s="39" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="M6" s="39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N6" s="41">
-        <v>501</v>
+        <v>1064</v>
       </c>
       <c r="O6" s="42" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q6" s="43">
-        <v>486</v>
+        <v>1027</v>
       </c>
       <c r="R6" s="44">
-        <v>649</v>
+        <v>1299</v>
       </c>
       <c r="S6" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T6" s="34" t="str">
-        <f>IF(ISBLANK(U6),SUBSTITUTE("18 %",".",","),IF(U6&lt;=486,SUBSTITUTE("5.7 %",".",","),IF(U6&lt;=501,SUBSTITUTE("7.1 %",".",","),IF(U6&lt;=556,SUBSTITUTE("7.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,8 %</v>
+        <f>IF(ISBLANK(U6),SUBSTITUTE("18 %",".",","),IF(U6&lt;=1027,SUBSTITUTE("5 %",".",","),IF(U6&lt;=1064,SUBSTITUTE("5.7 %",".",","),IF(U6&lt;=1103,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U6" s="46">
-        <v>556</v>
+        <v>1103</v>
       </c>
       <c r="V6"/>
       <c r="W6"/>
@@ -8117,68 +8303,68 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="33">
-        <v>135454215</v>
+        <v>135830775</v>
       </c>
       <c r="B7" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="34">
+        <v>29</v>
+      </c>
+      <c r="G7" s="35">
+        <v>46127.1270347338</v>
+      </c>
+      <c r="H7" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="38">
+        <v>805</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="41">
+        <v>788</v>
+      </c>
+      <c r="O7" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="34">
-        <v>10</v>
-      </c>
-      <c r="G7" s="35">
-        <v>46120.029930219913</v>
-      </c>
-      <c r="H7" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="38">
-        <v>642</v>
-      </c>
-      <c r="L7" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="M7" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="N7" s="41">
-        <v>621</v>
-      </c>
-      <c r="O7" s="42" t="s">
-        <v>88</v>
-      </c>
       <c r="P7" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q7" s="43">
-        <v>607</v>
+        <v>754</v>
       </c>
       <c r="R7" s="44">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="S7" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T7" s="34" t="str">
-        <f>IF(ISBLANK(U7),SUBSTITUTE("18 %",".",","),IF(U7&lt;=607,SUBSTITUTE("5 %",".",","),IF(U7&lt;=621,SUBSTITUTE("5.9 %",".",","),IF(U7&lt;=642,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>18 %</v>
-      </c>
-      <c r="U7" s="49">
-        <v>799</v>
+        <f>IF(ISBLANK(U7),SUBSTITUTE("18 %",".",","),IF(U7&lt;=754,SUBSTITUTE("5 %",".",","),IF(U7&lt;=788,SUBSTITUTE("5.7 %",".",","),IF(U7&lt;=805,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
+      </c>
+      <c r="U7" s="46">
+        <v>805</v>
       </c>
       <c r="V7"/>
       <c r="W7"/>
@@ -8196,68 +8382,68 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="33">
-        <v>135453334</v>
+        <v>135805419</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D8" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="34">
+        <v>5</v>
+      </c>
+      <c r="G8" s="35">
+        <v>46127.123233761573</v>
+      </c>
+      <c r="H8" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I8" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="J8" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="38">
+        <v>791</v>
+      </c>
+      <c r="L8" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="34">
-        <v>7</v>
-      </c>
-      <c r="G8" s="35">
-        <v>46120.029797129631</v>
-      </c>
-      <c r="H8" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I8" s="36" t="s">
+      <c r="M8" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="41">
+        <v>774</v>
+      </c>
+      <c r="O8" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="J8" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="38">
-        <v>642</v>
-      </c>
-      <c r="L8" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="M8" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" s="41">
-        <v>621</v>
-      </c>
-      <c r="O8" s="42" t="s">
-        <v>88</v>
-      </c>
       <c r="P8" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q8" s="43">
-        <v>607</v>
+        <v>742</v>
       </c>
       <c r="R8" s="44">
-        <v>899</v>
+        <v>939</v>
       </c>
       <c r="S8" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T8" s="34" t="str">
-        <f>IF(ISBLANK(U8),SUBSTITUTE("18 %",".",","),IF(U8&lt;=607,SUBSTITUTE("5 %",".",","),IF(U8&lt;=621,SUBSTITUTE("5.9 %",".",","),IF(U8&lt;=642,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U8),SUBSTITUTE("18 %",".",","),IF(U8&lt;=742,SUBSTITUTE("5 %",".",","),IF(U8&lt;=774,SUBSTITUTE("5.7 %",".",","),IF(U8&lt;=791,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U8" s="49">
-        <v>899</v>
+        <v>939</v>
       </c>
       <c r="V8"/>
       <c r="W8"/>
@@ -8275,68 +8461,68 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="33">
-        <v>135444766</v>
+        <v>135928378</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C9" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="34">
+        <v>30</v>
+      </c>
+      <c r="G9" s="35">
+        <v>46127.144389803238</v>
+      </c>
+      <c r="H9" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="38">
+        <v>507</v>
+      </c>
+      <c r="L9" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="41">
+        <v>489</v>
+      </c>
+      <c r="O9" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="34">
-        <v>10</v>
-      </c>
-      <c r="G9" s="35">
-        <v>46120.028521145832</v>
-      </c>
-      <c r="H9" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="K9" s="38">
-        <v>642</v>
-      </c>
-      <c r="L9" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="M9" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9" s="41">
-        <v>621</v>
-      </c>
-      <c r="O9" s="42" t="s">
-        <v>88</v>
-      </c>
       <c r="P9" s="42" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="43">
-        <v>607</v>
+        <v>474</v>
       </c>
       <c r="R9" s="44">
-        <v>799</v>
+        <v>649</v>
       </c>
       <c r="S9" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T9" s="34" t="str">
-        <f>IF(ISBLANK(U9),SUBSTITUTE("18 %",".",","),IF(U9&lt;=607,SUBSTITUTE("5 %",".",","),IF(U9&lt;=621,SUBSTITUTE("6 %",".",","),IF(U9&lt;=642,SUBSTITUTE("6.9 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>18 %</v>
-      </c>
-      <c r="U9" s="49">
-        <v>799</v>
+        <f>IF(ISBLANK(U9),SUBSTITUTE("18 %",".",","),IF(U9&lt;=474,SUBSTITUTE("5.7 %",".",","),IF(U9&lt;=489,SUBSTITUTE("6.4 %",".",","),IF(U9&lt;=507,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>7,1 %</v>
+      </c>
+      <c r="U9" s="46">
+        <v>507</v>
       </c>
       <c r="V9"/>
       <c r="W9"/>
@@ -8354,68 +8540,68 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="33">
-        <v>135487131</v>
+        <v>135893424</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F10" s="34">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G10" s="35">
-        <v>46120.035014490742</v>
+        <v>46127.138492129627</v>
       </c>
       <c r="H10" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J10" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="38">
+        <v>507</v>
+      </c>
+      <c r="L10" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="38">
-        <v>836</v>
-      </c>
-      <c r="L10" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="M10" s="39" t="s">
-        <v>64</v>
-      </c>
       <c r="N10" s="41">
-        <v>809</v>
+        <v>489</v>
       </c>
       <c r="O10" s="42" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="P10" s="42" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="43">
-        <v>800</v>
+        <v>474</v>
       </c>
       <c r="R10" s="44">
-        <v>899</v>
+        <v>649</v>
       </c>
       <c r="S10" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T10" s="34" t="str">
-        <f>IF(ISBLANK(U10),SUBSTITUTE("18 %",".",","),IF(U10&lt;=800,SUBSTITUTE("5 %",".",","),IF(U10&lt;=809,SUBSTITUTE("6.4 %",".",","),IF(U10&lt;=836,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U10),SUBSTITUTE("18 %",".",","),IF(U10&lt;=474,SUBSTITUTE("5.7 %",".",","),IF(U10&lt;=489,SUBSTITUTE("6.4 %",".",","),IF(U10&lt;=507,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>7,1 %</v>
       </c>
       <c r="U10" s="46">
-        <v>836</v>
+        <v>507</v>
       </c>
       <c r="V10"/>
       <c r="W10"/>
@@ -8433,68 +8619,68 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="33">
-        <v>135483334</v>
+        <v>135892887</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>94</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F11" s="34">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G11" s="35">
-        <v>46120.03443010417</v>
+        <v>46127.138384004633</v>
       </c>
       <c r="H11" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J11" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="38">
+        <v>507</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="38">
-        <v>836</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11" s="39" t="s">
-        <v>64</v>
-      </c>
       <c r="N11" s="41">
-        <v>809</v>
+        <v>489</v>
       </c>
       <c r="O11" s="42" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="P11" s="42" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="43">
-        <v>800</v>
+        <v>474</v>
       </c>
       <c r="R11" s="44">
-        <v>899</v>
+        <v>649</v>
       </c>
       <c r="S11" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T11" s="34" t="str">
-        <f>IF(ISBLANK(U11),SUBSTITUTE("18 %",".",","),IF(U11&lt;=800,SUBSTITUTE("5 %",".",","),IF(U11&lt;=809,SUBSTITUTE("6.4 %",".",","),IF(U11&lt;=836,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U11),SUBSTITUTE("18 %",".",","),IF(U11&lt;=474,SUBSTITUTE("5.7 %",".",","),IF(U11&lt;=489,SUBSTITUTE("6.4 %",".",","),IF(U11&lt;=507,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>7,1 %</v>
       </c>
       <c r="U11" s="46">
-        <v>836</v>
+        <v>507</v>
       </c>
       <c r="V11"/>
       <c r="W11"/>
@@ -8512,68 +8698,68 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="33">
-        <v>135450621</v>
+        <v>135789190</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F12" s="34">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G12" s="35">
-        <v>46120.029397546299</v>
+        <v>46127.120908078701</v>
       </c>
       <c r="H12" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="K12" s="38">
-        <v>604</v>
+        <v>505</v>
       </c>
       <c r="L12" s="39" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M12" s="39" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="N12" s="41">
-        <v>584</v>
+        <v>479</v>
       </c>
       <c r="O12" s="42" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="P12" s="42" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="43">
-        <v>577</v>
+        <v>455</v>
       </c>
       <c r="R12" s="44">
-        <v>899</v>
+        <v>649</v>
       </c>
       <c r="S12" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T12" s="34" t="str">
-        <f>IF(ISBLANK(U12),SUBSTITUTE("18 %",".",","),IF(U12&lt;=577,SUBSTITUTE("5.1 %",".",","),IF(U12&lt;=584,SUBSTITUTE("6.2 %",".",","),IF(U12&lt;=604,SUBSTITUTE("6.7 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>18 %</v>
-      </c>
-      <c r="U12" s="49">
-        <v>899</v>
+        <f>IF(ISBLANK(U12),SUBSTITUTE("18 %",".",","),IF(U12&lt;=455,SUBSTITUTE("5 %",".",","),IF(U12&lt;=479,SUBSTITUTE("5.7 %",".",","),IF(U12&lt;=505,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
+      </c>
+      <c r="U12" s="46">
+        <v>505</v>
       </c>
       <c r="V12"/>
       <c r="W12"/>
@@ -8591,68 +8777,68 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="33">
-        <v>135462397</v>
+        <v>135912471</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="34">
+        <v>20</v>
+      </c>
+      <c r="G13" s="35">
+        <v>46127.141759027778</v>
+      </c>
+      <c r="H13" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K13" s="38">
+        <v>576</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="M13" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="N13" s="41">
+        <v>547</v>
+      </c>
+      <c r="O13" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="34">
-        <v>11</v>
-      </c>
-      <c r="G13" s="35">
-        <v>46120.031164432869</v>
-      </c>
-      <c r="H13" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="K13" s="38">
-        <v>604</v>
-      </c>
-      <c r="L13" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="M13" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="N13" s="41">
-        <v>584</v>
-      </c>
-      <c r="O13" s="42" t="s">
-        <v>107</v>
-      </c>
       <c r="P13" s="42" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="43">
-        <v>577</v>
+        <v>519</v>
       </c>
       <c r="R13" s="44">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="S13" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T13" s="34" t="str">
-        <f>IF(ISBLANK(U13),SUBSTITUTE("18 %",".",","),IF(U13&lt;=577,SUBSTITUTE("5.1 %",".",","),IF(U13&lt;=584,SUBSTITUTE("6.2 %",".",","),IF(U13&lt;=604,SUBSTITUTE("6.7 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U13),SUBSTITUTE("18 %",".",","),IF(U13&lt;=519,SUBSTITUTE("5 %",".",","),IF(U13&lt;=547,SUBSTITUTE("5.9 %",".",","),IF(U13&lt;=576,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U13" s="49">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="V13"/>
       <c r="W13"/>
@@ -8670,68 +8856,68 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="33">
-        <v>135562302</v>
+        <v>135623780</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="34">
+        <v>8</v>
+      </c>
+      <c r="G14" s="35">
+        <v>46127.098548912043</v>
+      </c>
+      <c r="H14" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="38">
+        <v>652</v>
+      </c>
+      <c r="L14" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="M14" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="N14" s="41">
+        <v>631</v>
+      </c>
+      <c r="O14" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="P14" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="34">
-        <v>2</v>
-      </c>
-      <c r="G14" s="35">
-        <v>46120.055914884259</v>
-      </c>
-      <c r="H14" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" s="38">
-        <v>604</v>
-      </c>
-      <c r="L14" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="M14" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="N14" s="41">
-        <v>584</v>
-      </c>
-      <c r="O14" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="P14" s="42" t="s">
-        <v>87</v>
-      </c>
       <c r="Q14" s="43">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="R14" s="44">
-        <v>769</v>
+        <v>899</v>
       </c>
       <c r="S14" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T14" s="34" t="str">
-        <f>IF(ISBLANK(U14),SUBSTITUTE("18 %",".",","),IF(U14&lt;=571,SUBSTITUTE("5.9 %",".",","),IF(U14&lt;=584,SUBSTITUTE("7.3 %",".",","),IF(U14&lt;=604,SUBSTITUTE("8.3 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U14),SUBSTITUTE("18 %",".",","),IF(U14&lt;=610,SUBSTITUTE("5.2 %",".",","),IF(U14&lt;=631,SUBSTITUTE("6.3 %",".",","),IF(U14&lt;=652,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U14" s="49">
-        <v>769</v>
+        <v>899</v>
       </c>
       <c r="V14"/>
       <c r="W14"/>
@@ -8749,68 +8935,68 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="33">
-        <v>135300144</v>
+        <v>135623220</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D15" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="34">
+        <v>1</v>
+      </c>
+      <c r="G15" s="35">
+        <v>46127.098477094907</v>
+      </c>
+      <c r="H15" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="38">
+        <v>652</v>
+      </c>
+      <c r="L15" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="M15" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="N15" s="41">
+        <v>631</v>
+      </c>
+      <c r="O15" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="34">
-        <v>18</v>
-      </c>
-      <c r="G15" s="35">
-        <v>46120.002600150459</v>
-      </c>
-      <c r="H15" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="J15" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="K15" s="38">
-        <v>604</v>
-      </c>
-      <c r="L15" s="39" t="s">
+      <c r="P15" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="M15" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="N15" s="41">
-        <v>584</v>
-      </c>
-      <c r="O15" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="P15" s="42" t="s">
-        <v>64</v>
-      </c>
       <c r="Q15" s="43">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="R15" s="44">
-        <v>745.92999999999995</v>
+        <v>899</v>
       </c>
       <c r="S15" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T15" s="34" t="str">
-        <f>IF(ISBLANK(U15),SUBSTITUTE("18 %",".",","),IF(U15&lt;=571,SUBSTITUTE("6.4 %",".",","),IF(U15&lt;=584,SUBSTITUTE("7.4 %",".",","),IF(U15&lt;=604,SUBSTITUTE("8.2 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U15),SUBSTITUTE("18 %",".",","),IF(U15&lt;=610,SUBSTITUTE("5.3 %",".",","),IF(U15&lt;=631,SUBSTITUTE("6.3 %",".",","),IF(U15&lt;=652,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U15" s="49">
-        <v>745.92999999999995</v>
+        <v>899</v>
       </c>
       <c r="V15"/>
       <c r="W15"/>
@@ -8828,68 +9014,68 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="33">
-        <v>135534410</v>
+        <v>135866692</v>
       </c>
       <c r="B16" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="34">
+        <v>11</v>
+      </c>
+      <c r="G16" s="35">
+        <v>46127.134116388886</v>
+      </c>
+      <c r="H16" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="K16" s="38">
+        <v>577</v>
+      </c>
+      <c r="L16" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="M16" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="N16" s="41">
+        <v>548</v>
+      </c>
+      <c r="O16" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="34">
-        <v>24</v>
-      </c>
-      <c r="G16" s="35">
-        <v>46120.051850671298</v>
-      </c>
-      <c r="H16" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="K16" s="38">
-        <v>604</v>
-      </c>
-      <c r="L16" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="M16" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="N16" s="41">
-        <v>584</v>
-      </c>
-      <c r="O16" s="42" t="s">
-        <v>119</v>
-      </c>
       <c r="P16" s="42" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="Q16" s="43">
-        <v>571</v>
+        <v>520</v>
       </c>
       <c r="R16" s="44">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="S16" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T16" s="34" t="str">
-        <f>IF(ISBLANK(U16),SUBSTITUTE("18 %",".",","),IF(U16&lt;=571,SUBSTITUTE("5.8 %",".",","),IF(U16&lt;=584,SUBSTITUTE("7.1 %",".",","),IF(U16&lt;=604,SUBSTITUTE("8.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U16),SUBSTITUTE("18 %",".",","),IF(U16&lt;=520,SUBSTITUTE("5 %",".",","),IF(U16&lt;=548,SUBSTITUTE("5.8 %",".",","),IF(U16&lt;=577,SUBSTITUTE("6.6 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U16" s="49">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="V16"/>
       <c r="W16"/>
@@ -8907,68 +9093,68 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="33">
-        <v>135488313</v>
+        <v>135622952</v>
       </c>
       <c r="B17" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="34">
+        <v>23</v>
+      </c>
+      <c r="G17" s="35">
+        <v>46127.098442719907</v>
+      </c>
+      <c r="H17" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="J17" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="K17" s="38">
+        <v>601</v>
+      </c>
+      <c r="L17" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="M17" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="N17" s="41">
+        <v>581</v>
+      </c>
+      <c r="O17" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="E17" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="34">
-        <v>4</v>
-      </c>
-      <c r="G17" s="35">
-        <v>46120.035203368046</v>
-      </c>
-      <c r="H17" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I17" s="36" t="s">
+      <c r="P17" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="J17" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="K17" s="38">
-        <v>929</v>
-      </c>
-      <c r="L17" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="M17" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="N17" s="41">
-        <v>899</v>
-      </c>
-      <c r="O17" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="P17" s="42" t="s">
-        <v>89</v>
-      </c>
       <c r="Q17" s="43">
-        <v>879</v>
+        <v>561</v>
       </c>
       <c r="R17" s="44">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="S17" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T17" s="34" t="str">
-        <f>IF(ISBLANK(U17),SUBSTITUTE("18 %",".",","),IF(U17&lt;=879,SUBSTITUTE("5 %",".",","),IF(U17&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U17&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U17" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U17),SUBSTITUTE("18 %",".",","),IF(U17&lt;=561,SUBSTITUTE("5.6 %",".",","),IF(U17&lt;=581,SUBSTITUTE("6.7 %",".",","),IF(U17&lt;=601,SUBSTITUTE("7.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U17" s="49">
+        <v>799</v>
       </c>
       <c r="V17"/>
       <c r="W17"/>
@@ -8986,68 +9172,68 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="33">
-        <v>135485171</v>
+        <v>135951698</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C18" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="34" t="s">
-        <v>131</v>
-      </c>
       <c r="E18" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F18" s="34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="35">
-        <v>46120.034706689818</v>
+        <v>46127.149697037043</v>
       </c>
       <c r="H18" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J18" s="36" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="K18" s="38">
-        <v>929</v>
+        <v>516</v>
       </c>
       <c r="L18" s="39" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M18" s="39" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="N18" s="41">
-        <v>899</v>
+        <v>498</v>
       </c>
       <c r="O18" s="42" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="P18" s="42" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="Q18" s="43">
-        <v>879</v>
+        <v>481</v>
       </c>
       <c r="R18" s="44">
-        <v>999</v>
+        <v>769</v>
       </c>
       <c r="S18" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T18" s="34" t="str">
-        <f>IF(ISBLANK(U18),SUBSTITUTE("18 %",".",","),IF(U18&lt;=879,SUBSTITUTE("5 %",".",","),IF(U18&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U18&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U18" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U18),SUBSTITUTE("18 %",".",","),IF(U18&lt;=481,SUBSTITUTE("5.1 %",".",","),IF(U18&lt;=498,SUBSTITUTE("6.5 %",".",","),IF(U18&lt;=516,SUBSTITUTE("7.2 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U18" s="49">
+        <v>769</v>
       </c>
       <c r="V18"/>
       <c r="W18"/>
@@ -9065,68 +9251,68 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="33">
-        <v>135474770</v>
+        <v>135919241</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F19" s="34">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G19" s="35">
-        <v>46120.033097233798</v>
+        <v>46127.142783553238</v>
       </c>
       <c r="H19" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="J19" s="36" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="K19" s="38">
-        <v>929</v>
+        <v>523</v>
       </c>
       <c r="L19" s="39" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M19" s="39" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="N19" s="41">
-        <v>899</v>
+        <v>506</v>
       </c>
       <c r="O19" s="42" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="P19" s="42" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="Q19" s="43">
-        <v>879</v>
+        <v>489</v>
       </c>
       <c r="R19" s="44">
-        <v>999</v>
+        <v>745.92999999999995</v>
       </c>
       <c r="S19" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T19" s="34" t="str">
-        <f>IF(ISBLANK(U19),SUBSTITUTE("18 %",".",","),IF(U19&lt;=879,SUBSTITUTE("5 %",".",","),IF(U19&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U19&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U19" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U19),SUBSTITUTE("18 %",".",","),IF(U19&lt;=489,SUBSTITUTE("5.4 %",".",","),IF(U19&lt;=506,SUBSTITUTE("6.5 %",".",","),IF(U19&lt;=523,SUBSTITUTE("7.2 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U19" s="49">
+        <v>745.92999999999995</v>
       </c>
       <c r="V19"/>
       <c r="W19"/>
@@ -9144,68 +9330,68 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="33">
-        <v>135474673</v>
+        <v>135958339</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F20" s="34">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G20" s="35">
-        <v>46120.033080312503</v>
+        <v>46127.152192592592</v>
       </c>
       <c r="H20" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="K20" s="38">
-        <v>929</v>
+        <v>490</v>
       </c>
       <c r="L20" s="39" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="N20" s="41">
-        <v>899</v>
+        <v>474</v>
       </c>
       <c r="O20" s="42" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="P20" s="42" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="Q20" s="43">
-        <v>879</v>
+        <v>458</v>
       </c>
       <c r="R20" s="44">
-        <v>999</v>
+        <v>769</v>
       </c>
       <c r="S20" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T20" s="34" t="str">
-        <f>IF(ISBLANK(U20),SUBSTITUTE("18 %",".",","),IF(U20&lt;=879,SUBSTITUTE("5 %",".",","),IF(U20&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U20&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U20" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U20),SUBSTITUTE("18 %",".",","),IF(U20&lt;=458,SUBSTITUTE("5.7 %",".",","),IF(U20&lt;=474,SUBSTITUTE("6.8 %",".",","),IF(U20&lt;=490,SUBSTITUTE("7.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U20" s="49">
+        <v>769</v>
       </c>
       <c r="V20"/>
       <c r="W20"/>
@@ -9223,68 +9409,68 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="33">
-        <v>135470683</v>
+        <v>135915828</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E21" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="34">
+        <v>24</v>
+      </c>
+      <c r="G21" s="35">
+        <v>46127.142277418992</v>
+      </c>
+      <c r="H21" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I21" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="J21" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="K21" s="38">
+        <v>499</v>
+      </c>
+      <c r="L21" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="M21" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="N21" s="41">
+        <v>482</v>
+      </c>
+      <c r="O21" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="P21" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="34">
-        <v>4</v>
-      </c>
-      <c r="G21" s="35">
-        <v>46120.032455914348</v>
-      </c>
-      <c r="H21" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="J21" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="K21" s="38">
-        <v>929</v>
-      </c>
-      <c r="L21" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="N21" s="41">
-        <v>899</v>
-      </c>
-      <c r="O21" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="P21" s="42" t="s">
-        <v>89</v>
-      </c>
       <c r="Q21" s="43">
-        <v>879</v>
+        <v>465</v>
       </c>
       <c r="R21" s="44">
-        <v>999</v>
+        <v>769</v>
       </c>
       <c r="S21" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T21" s="34" t="str">
-        <f>IF(ISBLANK(U21),SUBSTITUTE("18 %",".",","),IF(U21&lt;=879,SUBSTITUTE("5 %",".",","),IF(U21&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U21&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U21" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U21),SUBSTITUTE("18 %",".",","),IF(U21&lt;=465,SUBSTITUTE("5.2 %",".",","),IF(U21&lt;=482,SUBSTITUTE("6.2 %",".",","),IF(U21&lt;=499,SUBSTITUTE("10.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U21" s="49">
+        <v>769</v>
       </c>
       <c r="V21"/>
       <c r="W21"/>
@@ -9302,55 +9488,55 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="33">
-        <v>135470612</v>
+        <v>135952004</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F22" s="34">
         <v>4</v>
       </c>
       <c r="G22" s="35">
-        <v>46120.032445567129</v>
+        <v>46127.149793391203</v>
       </c>
       <c r="H22" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>55</v>
+        <v>166</v>
       </c>
       <c r="K22" s="38">
-        <v>929</v>
+        <v>678</v>
       </c>
       <c r="L22" s="39" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="M22" s="39" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="N22" s="41">
-        <v>899</v>
+        <v>656</v>
       </c>
       <c r="O22" s="42" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="P22" s="42" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="Q22" s="43">
-        <v>879</v>
+        <v>635</v>
       </c>
       <c r="R22" s="44">
         <v>999</v>
@@ -9359,11 +9545,11 @@
         <v>58</v>
       </c>
       <c r="T22" s="34" t="str">
-        <f>IF(ISBLANK(U22),SUBSTITUTE("18 %",".",","),IF(U22&lt;=879,SUBSTITUTE("5 %",".",","),IF(U22&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U22&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U22" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U22),SUBSTITUTE("18 %",".",","),IF(U22&lt;=635,SUBSTITUTE("5.5 %",".",","),IF(U22&lt;=656,SUBSTITUTE("6.5 %",".",","),IF(U22&lt;=678,SUBSTITUTE("7.3 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U22" s="49">
+        <v>999</v>
       </c>
       <c r="V22"/>
       <c r="W22"/>
@@ -9381,55 +9567,55 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="33">
-        <v>135488495</v>
+        <v>135926729</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F23" s="34">
         <v>28</v>
       </c>
       <c r="G23" s="35">
-        <v>46120.035238622688</v>
+        <v>46127.144094456024</v>
       </c>
       <c r="H23" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I23" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="J23" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="K23" s="38">
+        <v>678</v>
+      </c>
+      <c r="L23" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="M23" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="N23" s="41">
+        <v>656</v>
+      </c>
+      <c r="O23" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="P23" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="J23" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="38">
-        <v>929</v>
-      </c>
-      <c r="L23" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="M23" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="N23" s="41">
-        <v>899</v>
-      </c>
-      <c r="O23" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="P23" s="42" t="s">
-        <v>89</v>
-      </c>
       <c r="Q23" s="43">
-        <v>879</v>
+        <v>635</v>
       </c>
       <c r="R23" s="44">
         <v>999</v>
@@ -9438,11 +9624,11 @@
         <v>58</v>
       </c>
       <c r="T23" s="34" t="str">
-        <f>IF(ISBLANK(U23),SUBSTITUTE("18 %",".",","),IF(U23&lt;=879,SUBSTITUTE("5 %",".",","),IF(U23&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U23&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U23" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U23),SUBSTITUTE("18 %",".",","),IF(U23&lt;=635,SUBSTITUTE("5.6 %",".",","),IF(U23&lt;=656,SUBSTITUTE("6.8 %",".",","),IF(U23&lt;=678,SUBSTITUTE("7.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U23" s="49">
+        <v>999</v>
       </c>
       <c r="V23"/>
       <c r="W23"/>
@@ -9460,55 +9646,55 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="33">
-        <v>135487033</v>
+        <v>135918837</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F24" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="35">
-        <v>46120.034997986113</v>
+        <v>46127.142724826394</v>
       </c>
       <c r="H24" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="J24" s="36" t="s">
-        <v>55</v>
+        <v>166</v>
       </c>
       <c r="K24" s="38">
-        <v>929</v>
+        <v>678</v>
       </c>
       <c r="L24" s="39" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="M24" s="39" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="N24" s="41">
-        <v>899</v>
+        <v>656</v>
       </c>
       <c r="O24" s="42" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="P24" s="42" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="Q24" s="43">
-        <v>879</v>
+        <v>635</v>
       </c>
       <c r="R24" s="44">
         <v>999</v>
@@ -9517,11 +9703,11 @@
         <v>58</v>
       </c>
       <c r="T24" s="34" t="str">
-        <f>IF(ISBLANK(U24),SUBSTITUTE("18 %",".",","),IF(U24&lt;=879,SUBSTITUTE("5 %",".",","),IF(U24&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U24&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U24" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U24),SUBSTITUTE("18 %",".",","),IF(U24&lt;=635,SUBSTITUTE("5.5 %",".",","),IF(U24&lt;=656,SUBSTITUTE("6.5 %",".",","),IF(U24&lt;=678,SUBSTITUTE("7.3 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U24" s="49">
+        <v>999</v>
       </c>
       <c r="V24"/>
       <c r="W24"/>
@@ -9539,55 +9725,55 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="33">
-        <v>135485052</v>
+        <v>135882668</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F25" s="34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" s="35">
-        <v>46120.034689652777</v>
+        <v>46127.136660810182</v>
       </c>
       <c r="H25" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="J25" s="36" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="K25" s="38">
-        <v>929</v>
+        <v>678</v>
       </c>
       <c r="L25" s="39" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="M25" s="39" t="s">
-        <v>64</v>
+        <v>175</v>
       </c>
       <c r="N25" s="41">
-        <v>899</v>
+        <v>656</v>
       </c>
       <c r="O25" s="42" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="P25" s="42" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="Q25" s="43">
-        <v>879</v>
+        <v>635</v>
       </c>
       <c r="R25" s="44">
         <v>999</v>
@@ -9596,11 +9782,11 @@
         <v>58</v>
       </c>
       <c r="T25" s="34" t="str">
-        <f>IF(ISBLANK(U25),SUBSTITUTE("18 %",".",","),IF(U25&lt;=879,SUBSTITUTE("5 %",".",","),IF(U25&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U25&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U25" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U25),SUBSTITUTE("18 %",".",","),IF(U25&lt;=635,SUBSTITUTE("5.1 %",".",","),IF(U25&lt;=656,SUBSTITUTE("6.1 %",".",","),IF(U25&lt;=678,SUBSTITUTE("6.9 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U25" s="49">
+        <v>999</v>
       </c>
       <c r="V25"/>
       <c r="W25"/>
@@ -9618,55 +9804,55 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="33">
-        <v>135474651</v>
+        <v>135826194</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F26" s="34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G26" s="35">
-        <v>46120.033075821761</v>
+        <v>46127.126126446761</v>
       </c>
       <c r="H26" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="J26" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K26" s="38">
-        <v>929</v>
+        <v>716</v>
       </c>
       <c r="L26" s="39" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="M26" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N26" s="41">
-        <v>899</v>
+        <v>692</v>
       </c>
       <c r="O26" s="42" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="P26" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q26" s="43">
-        <v>879</v>
+        <v>669</v>
       </c>
       <c r="R26" s="44">
         <v>999</v>
@@ -9675,11 +9861,11 @@
         <v>58</v>
       </c>
       <c r="T26" s="34" t="str">
-        <f>IF(ISBLANK(U26),SUBSTITUTE("18 %",".",","),IF(U26&lt;=879,SUBSTITUTE("5 %",".",","),IF(U26&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U26&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U26" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U26),SUBSTITUTE("18 %",".",","),IF(U26&lt;=669,SUBSTITUTE("5 %",".",","),IF(U26&lt;=692,SUBSTITUTE("5.7 %",".",","),IF(U26&lt;=716,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U26" s="49">
+        <v>999</v>
       </c>
       <c r="V26"/>
       <c r="W26"/>
@@ -9697,55 +9883,55 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="33">
-        <v>135474499</v>
+        <v>135799451</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F27" s="34">
         <v>4</v>
       </c>
       <c r="G27" s="35">
-        <v>46120.033051284721</v>
+        <v>46127.12230314815</v>
       </c>
       <c r="H27" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="J27" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K27" s="38">
-        <v>929</v>
+        <v>678</v>
       </c>
       <c r="L27" s="39" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="M27" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N27" s="41">
-        <v>899</v>
+        <v>656</v>
       </c>
       <c r="O27" s="42" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="P27" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q27" s="43">
-        <v>879</v>
+        <v>635</v>
       </c>
       <c r="R27" s="44">
         <v>999</v>
@@ -9754,11 +9940,11 @@
         <v>58</v>
       </c>
       <c r="T27" s="34" t="str">
-        <f>IF(ISBLANK(U27),SUBSTITUTE("18 %",".",","),IF(U27&lt;=879,SUBSTITUTE("5 %",".",","),IF(U27&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U27&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U27" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U27),SUBSTITUTE("18 %",".",","),IF(U27&lt;=635,SUBSTITUTE("5 %",".",","),IF(U27&lt;=656,SUBSTITUTE("5.7 %",".",","),IF(U27&lt;=678,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U27" s="49">
+        <v>999</v>
       </c>
       <c r="V27"/>
       <c r="W27"/>
@@ -9776,55 +9962,55 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="33">
-        <v>135472959</v>
+        <v>135816566</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F28" s="34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="35">
-        <v>46120.032813576392</v>
+        <v>46127.124831215267</v>
       </c>
       <c r="H28" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="J28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K28" s="38">
-        <v>929</v>
+        <v>677</v>
       </c>
       <c r="L28" s="39" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="M28" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N28" s="41">
-        <v>899</v>
+        <v>655</v>
       </c>
       <c r="O28" s="42" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="P28" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q28" s="43">
-        <v>879</v>
+        <v>635</v>
       </c>
       <c r="R28" s="44">
         <v>999</v>
@@ -9833,11 +10019,11 @@
         <v>58</v>
       </c>
       <c r="T28" s="34" t="str">
-        <f>IF(ISBLANK(U28),SUBSTITUTE("18 %",".",","),IF(U28&lt;=879,SUBSTITUTE("5 %",".",","),IF(U28&lt;=899,SUBSTITUTE("6.4 %",".",","),IF(U28&lt;=929,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U28" s="46">
-        <v>929</v>
+        <f>IF(ISBLANK(U28),SUBSTITUTE("18 %",".",","),IF(U28&lt;=635,SUBSTITUTE("5 %",".",","),IF(U28&lt;=655,SUBSTITUTE("5.7 %",".",","),IF(U28&lt;=677,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U28" s="49">
+        <v>999</v>
       </c>
       <c r="V28"/>
       <c r="W28"/>
@@ -9855,68 +10041,68 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="33">
-        <v>135459165</v>
+        <v>135797289</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F29" s="34">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G29" s="35">
-        <v>46120.030674618058</v>
+        <v>46127.122001342592</v>
       </c>
       <c r="H29" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="J29" s="36" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="K29" s="38">
-        <v>604</v>
+        <v>677</v>
       </c>
       <c r="L29" s="39" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="M29" s="39" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="N29" s="41">
-        <v>584</v>
+        <v>655</v>
       </c>
       <c r="O29" s="42" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="P29" s="42" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q29" s="43">
-        <v>577</v>
+        <v>635</v>
       </c>
       <c r="R29" s="44">
-        <v>872.02999999999997</v>
+        <v>999</v>
       </c>
       <c r="S29" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T29" s="34" t="str">
-        <f>IF(ISBLANK(U29),SUBSTITUTE("18 %",".",","),IF(U29&lt;=577,SUBSTITUTE("5.1 %",".",","),IF(U29&lt;=584,SUBSTITUTE("6.2 %",".",","),IF(U29&lt;=604,SUBSTITUTE("6.7 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U29),SUBSTITUTE("18 %",".",","),IF(U29&lt;=635,SUBSTITUTE("5 %",".",","),IF(U29&lt;=655,SUBSTITUTE("5.7 %",".",","),IF(U29&lt;=677,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U29" s="49">
-        <v>872.02999999999997</v>
+        <v>999</v>
       </c>
       <c r="V29"/>
       <c r="W29"/>
@@ -9934,68 +10120,68 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="33">
-        <v>135447485</v>
+        <v>135797267</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F30" s="34">
         <v>10</v>
       </c>
       <c r="G30" s="35">
-        <v>46120.028920243058</v>
+        <v>46127.121998240742</v>
       </c>
       <c r="H30" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="J30" s="36" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="K30" s="38">
-        <v>811</v>
+        <v>677</v>
       </c>
       <c r="L30" s="39" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="M30" s="39" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="N30" s="41">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="O30" s="42" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="P30" s="42" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q30" s="43">
-        <v>776</v>
+        <v>635</v>
       </c>
       <c r="R30" s="44">
-        <v>872.02999999999997</v>
+        <v>999</v>
       </c>
       <c r="S30" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T30" s="34" t="str">
-        <f>IF(ISBLANK(U30),SUBSTITUTE("18 %",".",","),IF(U30&lt;=776,SUBSTITUTE("5.1 %",".",","),IF(U30&lt;=785,SUBSTITUTE("6.2 %",".",","),IF(U30&lt;=811,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,8 %</v>
-      </c>
-      <c r="U30" s="46">
-        <v>811</v>
+        <f>IF(ISBLANK(U30),SUBSTITUTE("18 %",".",","),IF(U30&lt;=635,SUBSTITUTE("5 %",".",","),IF(U30&lt;=655,SUBSTITUTE("5.7 %",".",","),IF(U30&lt;=677,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U30" s="49">
+        <v>999</v>
       </c>
       <c r="V30"/>
       <c r="W30"/>
@@ -10013,68 +10199,68 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="33">
-        <v>135299386</v>
+        <v>135791071</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="E31" s="34" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F31" s="34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G31" s="35">
-        <v>46120.002399618053</v>
+        <v>46127.121164016207</v>
       </c>
       <c r="H31" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="J31" s="36" t="s">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="K31" s="38">
-        <v>604</v>
+        <v>677</v>
       </c>
       <c r="L31" s="39" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="M31" s="39" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="N31" s="41">
-        <v>584</v>
+        <v>655</v>
       </c>
       <c r="O31" s="42" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="P31" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q31" s="43">
-        <v>577</v>
+        <v>635</v>
       </c>
       <c r="R31" s="44">
-        <v>899</v>
+        <v>999</v>
       </c>
       <c r="S31" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T31" s="34" t="str">
-        <f>IF(ISBLANK(U31),SUBSTITUTE("18 %",".",","),IF(U31&lt;=577,SUBSTITUTE("5 %",".",","),IF(U31&lt;=584,SUBSTITUTE("6.1 %",".",","),IF(U31&lt;=604,SUBSTITUTE("6.6 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U31),SUBSTITUTE("18 %",".",","),IF(U31&lt;=635,SUBSTITUTE("5 %",".",","),IF(U31&lt;=655,SUBSTITUTE("5.7 %",".",","),IF(U31&lt;=677,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U31" s="49">
-        <v>899</v>
+        <v>999</v>
       </c>
       <c r="V31"/>
       <c r="W31"/>
@@ -10092,68 +10278,68 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="33">
-        <v>135298943</v>
+        <v>135791064</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F32" s="34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G32" s="35">
-        <v>46120.002320555563</v>
+        <v>46127.121162939817</v>
       </c>
       <c r="H32" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="J32" s="36" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="K32" s="38">
-        <v>604</v>
+        <v>677</v>
       </c>
       <c r="L32" s="39" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="M32" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="41">
+        <v>655</v>
+      </c>
+      <c r="O32" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="N32" s="41">
-        <v>584</v>
-      </c>
-      <c r="O32" s="42" t="s">
-        <v>107</v>
-      </c>
       <c r="P32" s="42" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="Q32" s="43">
-        <v>577</v>
+        <v>635</v>
       </c>
       <c r="R32" s="44">
-        <v>899</v>
+        <v>999</v>
       </c>
       <c r="S32" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T32" s="34" t="str">
-        <f>IF(ISBLANK(U32),SUBSTITUTE("18 %",".",","),IF(U32&lt;=577,SUBSTITUTE("5.2 %",".",","),IF(U32&lt;=584,SUBSTITUTE("6.3 %",".",","),IF(U32&lt;=604,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U32),SUBSTITUTE("18 %",".",","),IF(U32&lt;=635,SUBSTITUTE("5 %",".",","),IF(U32&lt;=655,SUBSTITUTE("5.7 %",".",","),IF(U32&lt;=677,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>18 %</v>
       </c>
       <c r="U32" s="49">
-        <v>899</v>
+        <v>999</v>
       </c>
       <c r="V32"/>
       <c r="W32"/>
@@ -10171,68 +10357,68 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="33">
-        <v>135581788</v>
+        <v>135623845</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E33" s="34" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="F33" s="34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" s="35">
-        <v>46120.059053263889</v>
+        <v>46127.09855707176</v>
       </c>
       <c r="H33" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="K33" s="38">
-        <v>1169</v>
+        <v>674</v>
       </c>
       <c r="L33" s="39" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="M33" s="39" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="N33" s="41">
-        <v>1143</v>
+        <v>653</v>
       </c>
       <c r="O33" s="42" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="P33" s="42" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="Q33" s="43">
-        <v>1130</v>
+        <v>632</v>
       </c>
       <c r="R33" s="44">
-        <v>1299</v>
+        <v>999</v>
       </c>
       <c r="S33" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T33" s="34" t="str">
-        <f>IF(ISBLANK(U33),SUBSTITUTE("18 %",".",","),IF(U33&lt;=1130,SUBSTITUTE("6.4 %",".",","),IF(U33&lt;=1143,SUBSTITUTE("7.8 %",".",","),IF(U33&lt;=1169,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
-      </c>
-      <c r="U33" s="46">
-        <v>1169</v>
+        <f>IF(ISBLANK(U33),SUBSTITUTE("18 %",".",","),IF(U33&lt;=632,SUBSTITUTE("5.6 %",".",","),IF(U33&lt;=653,SUBSTITUTE("6.7 %",".",","),IF(U33&lt;=674,SUBSTITUTE("7.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U33" s="49">
+        <v>999</v>
       </c>
       <c r="V33"/>
       <c r="W33"/>
@@ -10250,68 +10436,68 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="33">
-        <v>135578530</v>
+        <v>135936432</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="F34" s="34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G34" s="35">
-        <v>46120.058561018523</v>
+        <v>46127.14572335648</v>
       </c>
       <c r="H34" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>52</v>
+        <v>202</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="K34" s="38">
-        <v>1199</v>
+        <v>646</v>
       </c>
       <c r="L34" s="39" t="s">
-        <v>54</v>
+        <v>203</v>
       </c>
       <c r="M34" s="39" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N34" s="41">
-        <v>1182</v>
+        <v>624</v>
       </c>
       <c r="O34" s="42" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="P34" s="42" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="Q34" s="43">
-        <v>1143</v>
+        <v>603</v>
       </c>
       <c r="R34" s="44">
-        <v>1299</v>
+        <v>872.02999999999997</v>
       </c>
       <c r="S34" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T34" s="34" t="str">
-        <f>IF(ISBLANK(U34),SUBSTITUTE("18 %",".",","),IF(U34&lt;=1143,SUBSTITUTE("6.4 %",".",","),IF(U34&lt;=1182,SUBSTITUTE("7.8 %",".",","),IF(U34&lt;=1199,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
-      </c>
-      <c r="U34" s="46">
-        <v>1199</v>
+        <f>IF(ISBLANK(U34),SUBSTITUTE("18 %",".",","),IF(U34&lt;=603,SUBSTITUTE("5.4 %",".",","),IF(U34&lt;=624,SUBSTITUTE("6.4 %",".",","),IF(U34&lt;=646,SUBSTITUTE("7.2 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U34" s="49">
+        <v>872.02999999999997</v>
       </c>
       <c r="V34"/>
       <c r="W34"/>
@@ -10329,68 +10515,68 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="33">
-        <v>135578228</v>
+        <v>135913957</v>
       </c>
       <c r="B35" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="34">
+        <v>19</v>
+      </c>
+      <c r="G35" s="35">
+        <v>46127.141989039352</v>
+      </c>
+      <c r="H35" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I35" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="J35" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" s="38">
+        <v>538</v>
+      </c>
+      <c r="L35" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="M35" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="E35" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" s="34">
-        <v>5</v>
-      </c>
-      <c r="G35" s="35">
-        <v>46120.058513055563</v>
-      </c>
-      <c r="H35" s="35">
-        <v>46126.999305555553</v>
-      </c>
-      <c r="I35" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="J35" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="K35" s="38">
-        <v>1169</v>
-      </c>
-      <c r="L35" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="M35" s="39" t="s">
-        <v>63</v>
-      </c>
       <c r="N35" s="41">
-        <v>1143</v>
+        <v>511</v>
       </c>
       <c r="O35" s="42" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="P35" s="42" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="43">
-        <v>1130</v>
+        <v>485</v>
       </c>
       <c r="R35" s="44">
-        <v>1299</v>
+        <v>872.02999999999997</v>
       </c>
       <c r="S35" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T35" s="34" t="str">
-        <f>IF(ISBLANK(U35),SUBSTITUTE("18 %",".",","),IF(U35&lt;=1130,SUBSTITUTE("6.4 %",".",","),IF(U35&lt;=1143,SUBSTITUTE("7.8 %",".",","),IF(U35&lt;=1169,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
-      </c>
-      <c r="U35" s="46">
-        <v>1169</v>
+        <f>IF(ISBLANK(U35),SUBSTITUTE("18 %",".",","),IF(U35&lt;=485,SUBSTITUTE("5.1 %",".",","),IF(U35&lt;=511,SUBSTITUTE("6.1 %",".",","),IF(U35&lt;=538,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U35" s="49">
+        <v>872.02999999999997</v>
       </c>
       <c r="V35"/>
       <c r="W35"/>
@@ -10408,68 +10594,68 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="33">
-        <v>135559453</v>
+        <v>135909084</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="E36" s="34" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="F36" s="34">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G36" s="35">
-        <v>46120.055503668977</v>
+        <v>46127.141194479169</v>
       </c>
       <c r="H36" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I36" s="36" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="J36" s="36" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="K36" s="38">
-        <v>1199</v>
+        <v>576</v>
       </c>
       <c r="L36" s="39" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="M36" s="39" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="N36" s="41">
-        <v>1182</v>
+        <v>547</v>
       </c>
       <c r="O36" s="42" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="P36" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q36" s="43">
-        <v>1143</v>
+        <v>519</v>
       </c>
       <c r="R36" s="44">
-        <v>1299</v>
+        <v>899</v>
       </c>
       <c r="S36" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T36" s="34" t="str">
-        <f>IF(ISBLANK(U36),SUBSTITUTE("18 %",".",","),IF(U36&lt;=1143,SUBSTITUTE("6.4 %",".",","),IF(U36&lt;=1182,SUBSTITUTE("7.8 %",".",","),IF(U36&lt;=1199,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
-      </c>
-      <c r="U36" s="46">
-        <v>1199</v>
+        <f>IF(ISBLANK(U36),SUBSTITUTE("18 %",".",","),IF(U36&lt;=519,SUBSTITUTE("5 %",".",","),IF(U36&lt;=547,SUBSTITUTE("5.9 %",".",","),IF(U36&lt;=576,SUBSTITUTE("6.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U36" s="49">
+        <v>899</v>
       </c>
       <c r="V36"/>
       <c r="W36"/>
@@ -10487,68 +10673,68 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="33">
-        <v>135559281</v>
+        <v>135873985</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="F37" s="34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G37" s="35">
-        <v>46120.055480868054</v>
+        <v>46127.135337164349</v>
       </c>
       <c r="H37" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="J37" s="36" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="K37" s="38">
-        <v>1169</v>
+        <v>576</v>
       </c>
       <c r="L37" s="39" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="M37" s="39" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="N37" s="41">
-        <v>1143</v>
+        <v>547</v>
       </c>
       <c r="O37" s="42" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="P37" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q37" s="43">
-        <v>1130</v>
+        <v>519</v>
       </c>
       <c r="R37" s="44">
-        <v>1299</v>
+        <v>899</v>
       </c>
       <c r="S37" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T37" s="34" t="str">
-        <f>IF(ISBLANK(U37),SUBSTITUTE("18 %",".",","),IF(U37&lt;=1130,SUBSTITUTE("6.4 %",".",","),IF(U37&lt;=1143,SUBSTITUTE("7.8 %",".",","),IF(U37&lt;=1169,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
-      </c>
-      <c r="U37" s="46">
-        <v>1169</v>
+        <f>IF(ISBLANK(U37),SUBSTITUTE("18 %",".",","),IF(U37&lt;=519,SUBSTITUTE("5 %",".",","),IF(U37&lt;=547,SUBSTITUTE("5.8 %",".",","),IF(U37&lt;=576,SUBSTITUTE("6.7 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U37" s="49">
+        <v>899</v>
       </c>
       <c r="V37"/>
       <c r="W37"/>
@@ -10566,55 +10752,55 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="33">
-        <v>135305076</v>
+        <v>135942264</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="E38" s="34" t="s">
         <v>51</v>
       </c>
       <c r="F38" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G38" s="35">
-        <v>46120.003458715277</v>
+        <v>46127.147139652778</v>
       </c>
       <c r="H38" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="J38" s="36" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K38" s="38">
-        <v>1169</v>
+        <v>1208</v>
       </c>
       <c r="L38" s="39" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="M38" s="39" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="N38" s="41">
+        <v>1182</v>
+      </c>
+      <c r="O38" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="P38" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q38" s="43">
         <v>1143</v>
-      </c>
-      <c r="O38" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="P38" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q38" s="43">
-        <v>1130</v>
       </c>
       <c r="R38" s="44">
         <v>1299</v>
@@ -10623,11 +10809,11 @@
         <v>58</v>
       </c>
       <c r="T38" s="34" t="str">
-        <f>IF(ISBLANK(U38),SUBSTITUTE("18 %",".",","),IF(U38&lt;=1130,SUBSTITUTE("6.2 %",".",","),IF(U38&lt;=1143,SUBSTITUTE("7.4 %",".",","),IF(U38&lt;=1169,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U38),SUBSTITUTE("18 %",".",","),IF(U38&lt;=1143,SUBSTITUTE("5.7 %",".",","),IF(U38&lt;=1182,SUBSTITUTE("6.4 %",".",","),IF(U38&lt;=1208,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>7,1 %</v>
       </c>
       <c r="U38" s="46">
-        <v>1169</v>
+        <v>1208</v>
       </c>
       <c r="V38"/>
       <c r="W38"/>
@@ -10645,68 +10831,68 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="33">
-        <v>135577225</v>
+        <v>135905219</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="E39" s="34" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="F39" s="34">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G39" s="35">
-        <v>46120.058366261583</v>
+        <v>46127.140506724543</v>
       </c>
       <c r="H39" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="J39" s="36" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K39" s="38">
-        <v>849</v>
+        <v>1208</v>
       </c>
       <c r="L39" s="39" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="M39" s="39" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N39" s="41">
-        <v>845</v>
+        <v>1182</v>
       </c>
       <c r="O39" s="42" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="P39" s="42" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="Q39" s="43">
-        <v>809</v>
+        <v>1143</v>
       </c>
       <c r="R39" s="44">
-        <v>899</v>
+        <v>1299</v>
       </c>
       <c r="S39" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T39" s="34" t="str">
-        <f>IF(ISBLANK(U39),SUBSTITUTE("18 %",".",","),IF(U39&lt;=809,SUBSTITUTE("6.4 %",".",","),IF(U39&lt;=845,SUBSTITUTE("7.8 %",".",","),IF(U39&lt;=849,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U39),SUBSTITUTE("18 %",".",","),IF(U39&lt;=1143,SUBSTITUTE("5.7 %",".",","),IF(U39&lt;=1182,SUBSTITUTE("6.4 %",".",","),IF(U39&lt;=1208,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>7,1 %</v>
       </c>
       <c r="U39" s="46">
-        <v>849</v>
+        <v>1208</v>
       </c>
       <c r="V39"/>
       <c r="W39"/>
@@ -10724,68 +10910,68 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="33">
-        <v>135482870</v>
+        <v>135895318</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="F40" s="34">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G40" s="35">
-        <v>46120.034355555559</v>
+        <v>46127.138859317129</v>
       </c>
       <c r="H40" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="J40" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K40" s="38">
+        <v>1208</v>
+      </c>
+      <c r="L40" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="K40" s="38">
-        <v>836</v>
-      </c>
-      <c r="L40" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="M40" s="39" t="s">
-        <v>64</v>
-      </c>
       <c r="N40" s="41">
-        <v>809</v>
+        <v>1182</v>
       </c>
       <c r="O40" s="42" t="s">
-        <v>192</v>
+        <v>56</v>
       </c>
       <c r="P40" s="42" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="Q40" s="43">
-        <v>791</v>
+        <v>1143</v>
       </c>
       <c r="R40" s="44">
-        <v>899</v>
+        <v>1299</v>
       </c>
       <c r="S40" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T40" s="34" t="str">
-        <f>IF(ISBLANK(U40),SUBSTITUTE("18 %",".",","),IF(U40&lt;=791,SUBSTITUTE("5 %",".",","),IF(U40&lt;=809,SUBSTITUTE("6.4 %",".",","),IF(U40&lt;=836,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U40),SUBSTITUTE("18 %",".",","),IF(U40&lt;=1143,SUBSTITUTE("5.7 %",".",","),IF(U40&lt;=1182,SUBSTITUTE("6.4 %",".",","),IF(U40&lt;=1208,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>7,1 %</v>
       </c>
       <c r="U40" s="46">
-        <v>836</v>
+        <v>1208</v>
       </c>
       <c r="V40"/>
       <c r="W40"/>
@@ -10803,68 +10989,68 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="33">
-        <v>135560126</v>
+        <v>135842550</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>51</v>
       </c>
       <c r="F41" s="34">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G41" s="35">
-        <v>46120.05560349537</v>
+        <v>46127.129812280087</v>
       </c>
       <c r="H41" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="J41" s="36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K41" s="38">
-        <v>1034</v>
+        <v>1088</v>
       </c>
       <c r="L41" s="39" t="s">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="M41" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N41" s="41">
-        <v>1011</v>
+        <v>1049</v>
       </c>
       <c r="O41" s="42" t="s">
-        <v>198</v>
+        <v>64</v>
       </c>
       <c r="P41" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q41" s="43">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="R41" s="44">
-        <v>1149</v>
+        <v>1299</v>
       </c>
       <c r="S41" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T41" s="34" t="str">
-        <f>IF(ISBLANK(U41),SUBSTITUTE("18 %",".",","),IF(U41&lt;=1000,SUBSTITUTE("6.4 %",".",","),IF(U41&lt;=1011,SUBSTITUTE("7.8 %",".",","),IF(U41&lt;=1034,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U41),SUBSTITUTE("18 %",".",","),IF(U41&lt;=1013,SUBSTITUTE("5 %",".",","),IF(U41&lt;=1049,SUBSTITUTE("5.7 %",".",","),IF(U41&lt;=1088,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U41" s="46">
-        <v>1034</v>
+        <v>1088</v>
       </c>
       <c r="V41"/>
       <c r="W41"/>
@@ -10882,68 +11068,68 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="33">
-        <v>135452548</v>
+        <v>135840133</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="F42" s="34">
         <v>5</v>
       </c>
       <c r="G42" s="35">
-        <v>46120.029680243053</v>
+        <v>46127.129365960653</v>
       </c>
       <c r="H42" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>203</v>
+        <v>62</v>
       </c>
       <c r="J42" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K42" s="38">
-        <v>318</v>
+        <v>1088</v>
       </c>
       <c r="L42" s="39" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="M42" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="41">
+        <v>1049</v>
+      </c>
+      <c r="O42" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="N42" s="41">
-        <v>315</v>
-      </c>
-      <c r="O42" s="42" t="s">
-        <v>205</v>
-      </c>
       <c r="P42" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q42" s="43">
-        <v>304</v>
+        <v>1013</v>
       </c>
       <c r="R42" s="44">
-        <v>559</v>
+        <v>1299</v>
       </c>
       <c r="S42" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T42" s="34" t="str">
-        <f>IF(ISBLANK(U42),SUBSTITUTE("18 %",".",","),IF(U42&lt;=304,SUBSTITUTE("5 %",".",","),IF(U42&lt;=315,SUBSTITUTE("6.4 %",".",","),IF(U42&lt;=318,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>18 %</v>
-      </c>
-      <c r="U42" s="49">
-        <v>559</v>
+        <f>IF(ISBLANK(U42),SUBSTITUTE("18 %",".",","),IF(U42&lt;=1013,SUBSTITUTE("5 %",".",","),IF(U42&lt;=1049,SUBSTITUTE("5.7 %",".",","),IF(U42&lt;=1088,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
+      </c>
+      <c r="U42" s="46">
+        <v>1088</v>
       </c>
       <c r="V42"/>
       <c r="W42"/>
@@ -10961,68 +11147,68 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="33">
-        <v>135580721</v>
+        <v>135834879</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E43" s="34" t="s">
         <v>51</v>
       </c>
       <c r="F43" s="34">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G43" s="35">
-        <v>46120.058891655091</v>
+        <v>46127.128077696761</v>
       </c>
       <c r="H43" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>132</v>
+        <v>227</v>
       </c>
       <c r="J43" s="36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K43" s="38">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="L43" s="39" t="s">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="M43" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N43" s="41">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="O43" s="42" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="P43" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q43" s="43">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="R43" s="44">
-        <v>999</v>
+        <v>1299</v>
       </c>
       <c r="S43" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T43" s="34" t="str">
-        <f>IF(ISBLANK(U43),SUBSTITUTE("18 %",".",","),IF(U43&lt;=879,SUBSTITUTE("6.4 %",".",","),IF(U43&lt;=899,SUBSTITUTE("7.8 %",".",","),IF(U43&lt;=929,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U43),SUBSTITUTE("18 %",".",","),IF(U43&lt;=875,SUBSTITUTE("5 %",".",","),IF(U43&lt;=904,SUBSTITUTE("5.7 %",".",","),IF(U43&lt;=935,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U43" s="46">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="V43"/>
       <c r="W43"/>
@@ -11040,68 +11226,68 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="33">
-        <v>135578578</v>
+        <v>135818221</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E44" s="34" t="s">
         <v>51</v>
       </c>
       <c r="F44" s="34">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G44" s="35">
-        <v>46120.058568125001</v>
+        <v>46127.125051134259</v>
       </c>
       <c r="H44" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I44" s="36" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="J44" s="36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K44" s="38">
-        <v>929</v>
+        <v>1103</v>
       </c>
       <c r="L44" s="39" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="M44" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N44" s="41">
-        <v>899</v>
+        <v>1064</v>
       </c>
       <c r="O44" s="42" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="P44" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q44" s="43">
-        <v>879</v>
+        <v>1027</v>
       </c>
       <c r="R44" s="44">
-        <v>999</v>
+        <v>1299</v>
       </c>
       <c r="S44" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T44" s="34" t="str">
-        <f>IF(ISBLANK(U44),SUBSTITUTE("18 %",".",","),IF(U44&lt;=879,SUBSTITUTE("6.4 %",".",","),IF(U44&lt;=899,SUBSTITUTE("7.8 %",".",","),IF(U44&lt;=929,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U44),SUBSTITUTE("18 %",".",","),IF(U44&lt;=1027,SUBSTITUTE("5 %",".",","),IF(U44&lt;=1064,SUBSTITUTE("5.7 %",".",","),IF(U44&lt;=1103,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U44" s="46">
-        <v>929</v>
+        <v>1103</v>
       </c>
       <c r="V44"/>
       <c r="W44"/>
@@ -11119,68 +11305,68 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="33">
-        <v>135556432</v>
+        <v>135810176</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="E45" s="34" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="F45" s="34">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45" s="35">
-        <v>46120.055017766201</v>
+        <v>46127.123920601851</v>
       </c>
       <c r="H45" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>132</v>
+        <v>234</v>
       </c>
       <c r="J45" s="36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K45" s="38">
-        <v>929</v>
+        <v>863</v>
       </c>
       <c r="L45" s="39" t="s">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="M45" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N45" s="41">
+        <v>845</v>
+      </c>
+      <c r="O45" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="P45" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q45" s="43">
+        <v>809</v>
+      </c>
+      <c r="R45" s="44">
         <v>899</v>
-      </c>
-      <c r="O45" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="P45" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q45" s="43">
-        <v>879</v>
-      </c>
-      <c r="R45" s="44">
-        <v>999</v>
       </c>
       <c r="S45" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T45" s="34" t="str">
-        <f>IF(ISBLANK(U45),SUBSTITUTE("18 %",".",","),IF(U45&lt;=879,SUBSTITUTE("6.4 %",".",","),IF(U45&lt;=899,SUBSTITUTE("7.8 %",".",","),IF(U45&lt;=929,SUBSTITUTE("8.5 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>8,5 %</v>
+        <f>IF(ISBLANK(U45),SUBSTITUTE("18 %",".",","),IF(U45&lt;=809,SUBSTITUTE("5 %",".",","),IF(U45&lt;=845,SUBSTITUTE("5.7 %",".",","),IF(U45&lt;=863,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
       </c>
       <c r="U45" s="46">
-        <v>929</v>
+        <v>863</v>
       </c>
       <c r="V45"/>
       <c r="W45"/>
@@ -11198,69 +11384,71 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="33">
-        <v>135540958</v>
+        <v>135796311</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="F46" s="34">
         <v>20</v>
       </c>
       <c r="G46" s="35">
-        <v>46120.052760706021</v>
+        <v>46127.121863553242</v>
       </c>
       <c r="H46" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K46" s="38">
-        <v>775</v>
+        <v>617</v>
       </c>
       <c r="L46" s="39" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N46" s="41">
-        <v>766</v>
+        <v>597</v>
       </c>
       <c r="O46" s="42" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="P46" s="42" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q46" s="43">
-        <v>679</v>
+        <v>578</v>
       </c>
       <c r="R46" s="44">
-        <v>870</v>
+        <v>899</v>
       </c>
       <c r="S46" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T46" s="34" t="str">
-        <f>IF(ISBLANK(U46),SUBSTITUTE("18 %",".",","),IF(U46&lt;=679,SUBSTITUTE("5.7 %",".",","),IF(U46&lt;=766,SUBSTITUTE("7.1 %",".",","),IF(U46&lt;=775,SUBSTITUTE("7.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>7,1 %</v>
-      </c>
-      <c r="U46" s="50">
-        <v>766</v>
-      </c>
+        <f>IF(ISBLANK(U46),SUBSTITUTE("18 %",".",","),IF(U46&lt;=578,SUBSTITUTE("5 %",".",","),IF(U46&lt;=597,SUBSTITUTE("5.7 %",".",","),IF(U46&lt;=617,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U46" s="49">
+        <v>899</v>
+      </c>
+      <c r="V46"/>
+      <c r="W46"/>
       <c r="X46" s="48"/>
       <c r="Y46" s="48"/>
       <c r="Z46" s="48"/>
@@ -11275,69 +11463,71 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="33">
-        <v>135535956</v>
+        <v>135833444</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="F47" s="34">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G47" s="35">
-        <v>46120.052064351847</v>
+        <v>46127.127659953701</v>
       </c>
       <c r="H47" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="J47" s="36" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K47" s="38">
-        <v>766</v>
+        <v>957</v>
       </c>
       <c r="L47" s="39" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="M47" s="39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N47" s="41">
-        <v>743</v>
+        <v>941</v>
       </c>
       <c r="O47" s="42" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="P47" s="42" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q47" s="43">
-        <v>679</v>
+        <v>929</v>
       </c>
       <c r="R47" s="44">
-        <v>870</v>
+        <v>1199</v>
       </c>
       <c r="S47" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T47" s="34" t="str">
-        <f>IF(ISBLANK(U47),SUBSTITUTE("18 %",".",","),IF(U47&lt;=679,SUBSTITUTE("5.7 %",".",","),IF(U47&lt;=743,SUBSTITUTE("7.1 %",".",","),IF(U47&lt;=766,SUBSTITUTE("7.8 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>18 %</v>
-      </c>
-      <c r="U47" s="51">
-        <v>870</v>
-      </c>
+        <f>IF(ISBLANK(U47),SUBSTITUTE("18 %",".",","),IF(U47&lt;=929,SUBSTITUTE("5 %",".",","),IF(U47&lt;=941,SUBSTITUTE("5.7 %",".",","),IF(U47&lt;=957,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>6,4 %</v>
+      </c>
+      <c r="U47" s="46">
+        <v>957</v>
+      </c>
+      <c r="V47"/>
+      <c r="W47"/>
       <c r="X47" s="48"/>
       <c r="Y47" s="48"/>
       <c r="Z47" s="48"/>
@@ -11352,69 +11542,71 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="33">
-        <v>135468185</v>
+        <v>135826613</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E48" s="34" t="s">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="F48" s="34">
         <v>20</v>
       </c>
       <c r="G48" s="35">
-        <v>46120.032043171297</v>
+        <v>46127.126182430547</v>
       </c>
       <c r="H48" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="J48" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K48" s="38">
-        <v>809</v>
+        <v>832</v>
       </c>
       <c r="L48" s="39" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N48" s="41">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="O48" s="42" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="P48" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q48" s="43">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="R48" s="44">
-        <v>870</v>
+        <v>1149</v>
       </c>
       <c r="S48" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T48" s="34" t="str">
-        <f>IF(ISBLANK(U48),SUBSTITUTE("18 %",".",","),IF(U48&lt;=766,SUBSTITUTE("5 %",".",","),IF(U48&lt;=783,SUBSTITUTE("6.4 %",".",","),IF(U48&lt;=809,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
-      </c>
-      <c r="U48" s="50">
-        <v>783</v>
-      </c>
+        <f>IF(ISBLANK(U48),SUBSTITUTE("18 %",".",","),IF(U48&lt;=778,SUBSTITUTE("5 %",".",","),IF(U48&lt;=804,SUBSTITUTE("5.7 %",".",","),IF(U48&lt;=832,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U48" s="49">
+        <v>1149</v>
+      </c>
+      <c r="V48"/>
+      <c r="W48"/>
       <c r="X48" s="48"/>
       <c r="Y48" s="48"/>
       <c r="Z48" s="48"/>
@@ -11429,69 +11621,71 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="33">
-        <v>135477626</v>
+        <v>135794143</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="F49" s="34">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G49" s="35">
-        <v>46120.033541435187</v>
+        <v>46127.121572129632</v>
       </c>
       <c r="H49" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="J49" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K49" s="38">
-        <v>586</v>
+        <v>312</v>
       </c>
       <c r="L49" s="39" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="M49" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N49" s="41">
-        <v>567</v>
+        <v>311</v>
       </c>
       <c r="O49" s="42" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="P49" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q49" s="43">
-        <v>554</v>
+        <v>307</v>
       </c>
       <c r="R49" s="44">
-        <v>630</v>
+        <v>345</v>
       </c>
       <c r="S49" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T49" s="34" t="str">
-        <f>IF(ISBLANK(U49),SUBSTITUTE("18 %",".",","),IF(U49&lt;=554,SUBSTITUTE("5 %",".",","),IF(U49&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U49&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
-      </c>
-      <c r="U49" s="50">
-        <v>567</v>
-      </c>
+        <f>IF(ISBLANK(U49),SUBSTITUTE("18 %",".",","),IF(U49&lt;=307,SUBSTITUTE("5 %",".",","),IF(U49&lt;=311,SUBSTITUTE("5.7 %",".",","),IF(U49&lt;=312,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U49" s="49">
+        <v>345</v>
+      </c>
+      <c r="V49"/>
+      <c r="W49"/>
       <c r="X49" s="48"/>
       <c r="Y49" s="48"/>
       <c r="Z49" s="48"/>
@@ -11506,69 +11700,71 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="33">
-        <v>135476847</v>
+        <v>135888697</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F50" s="34">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G50" s="35">
-        <v>46120.033414953701</v>
+        <v>46127.137590347222</v>
       </c>
       <c r="H50" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I50" s="36" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="J50" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K50" s="38">
+        <v>322</v>
+      </c>
+      <c r="L50" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="M50" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="K50" s="38">
-        <v>586</v>
-      </c>
-      <c r="L50" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="M50" s="39" t="s">
-        <v>64</v>
-      </c>
       <c r="N50" s="41">
-        <v>567</v>
+        <v>318</v>
       </c>
       <c r="O50" s="42" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="P50" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q50" s="43">
-        <v>554</v>
+        <v>310</v>
       </c>
       <c r="R50" s="44">
-        <v>630</v>
+        <v>559</v>
       </c>
       <c r="S50" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T50" s="34" t="str">
-        <f>IF(ISBLANK(U50),SUBSTITUTE("18 %",".",","),IF(U50&lt;=554,SUBSTITUTE("5 %",".",","),IF(U50&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U50&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
-      </c>
-      <c r="U50" s="50">
-        <v>567</v>
-      </c>
+        <f>IF(ISBLANK(U50),SUBSTITUTE("18 %",".",","),IF(U50&lt;=310,SUBSTITUTE("5 %",".",","),IF(U50&lt;=318,SUBSTITUTE("6.4 %",".",","),IF(U50&lt;=322,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U50" s="49">
+        <v>559</v>
+      </c>
+      <c r="V50"/>
+      <c r="W50"/>
       <c r="X50" s="48"/>
       <c r="Y50" s="48"/>
       <c r="Z50" s="48"/>
@@ -11583,69 +11779,71 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="33">
-        <v>135476800</v>
+        <v>135918181</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F51" s="34">
         <v>20</v>
       </c>
       <c r="G51" s="35">
-        <v>46120.03340709491</v>
+        <v>46127.142626342589</v>
       </c>
       <c r="H51" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="J51" s="36" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="K51" s="38">
-        <v>586</v>
+        <v>112</v>
       </c>
       <c r="L51" s="39" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="M51" s="39" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="N51" s="41">
-        <v>567</v>
+        <v>110</v>
       </c>
       <c r="O51" s="42" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="P51" s="42" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="Q51" s="43">
-        <v>554</v>
+        <v>97</v>
       </c>
       <c r="R51" s="44">
-        <v>630</v>
+        <v>199</v>
       </c>
       <c r="S51" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T51" s="34" t="str">
-        <f>IF(ISBLANK(U51),SUBSTITUTE("18 %",".",","),IF(U51&lt;=554,SUBSTITUTE("5 %",".",","),IF(U51&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U51&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
-      </c>
-      <c r="U51" s="50">
-        <v>567</v>
-      </c>
+        <f>IF(ISBLANK(U51),SUBSTITUTE("18 %",".",","),IF(U51&lt;=97,SUBSTITUTE("6.2 %",".",","),IF(U51&lt;=110,SUBSTITUTE("7.2 %",".",","),IF(U51&lt;=112,SUBSTITUTE("7.7 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U51" s="49">
+        <v>199</v>
+      </c>
+      <c r="V51"/>
+      <c r="W51"/>
       <c r="X51" s="48"/>
       <c r="Y51" s="48"/>
       <c r="Z51" s="48"/>
@@ -11660,68 +11858,68 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="33">
-        <v>135474459</v>
+        <v>135938116</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F52" s="34">
         <v>20</v>
       </c>
       <c r="G52" s="35">
-        <v>46120.033045127311</v>
+        <v>46127.145982754628</v>
       </c>
       <c r="H52" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>231</v>
+        <v>276</v>
       </c>
       <c r="J52" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="K52" s="38">
+        <v>783</v>
+      </c>
+      <c r="L52" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="M52" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="K52" s="38">
-        <v>586</v>
-      </c>
-      <c r="L52" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="M52" s="39" t="s">
-        <v>64</v>
-      </c>
       <c r="N52" s="41">
-        <v>567</v>
+        <v>766</v>
       </c>
       <c r="O52" s="42" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="P52" s="42" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="Q52" s="43">
-        <v>554</v>
+        <v>679</v>
       </c>
       <c r="R52" s="44">
-        <v>630</v>
+        <v>870</v>
       </c>
       <c r="S52" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T52" s="34" t="str">
-        <f>IF(ISBLANK(U52),SUBSTITUTE("18 %",".",","),IF(U52&lt;=554,SUBSTITUTE("5 %",".",","),IF(U52&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U52&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <f>IF(ISBLANK(U52),SUBSTITUTE("18 %",".",","),IF(U52&lt;=679,SUBSTITUTE("5.7 %",".",","),IF(U52&lt;=766,SUBSTITUTE("6.4 %",".",","),IF(U52&lt;=783,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
         <v>6,4 %</v>
       </c>
       <c r="U52" s="50">
-        <v>567</v>
+        <v>766</v>
       </c>
       <c r="X52" s="48"/>
       <c r="Y52" s="48"/>
@@ -11737,68 +11935,68 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="33">
-        <v>135474450</v>
+        <v>135798824</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F53" s="34">
         <v>20</v>
       </c>
       <c r="G53" s="35">
-        <v>46120.033043634263</v>
+        <v>46127.122210983798</v>
       </c>
       <c r="H53" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="J53" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K53" s="38">
-        <v>586</v>
+        <v>809</v>
       </c>
       <c r="L53" s="39" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="M53" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N53" s="41">
-        <v>567</v>
+        <v>783</v>
       </c>
       <c r="O53" s="42" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="P53" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q53" s="43">
-        <v>554</v>
+        <v>766</v>
       </c>
       <c r="R53" s="44">
-        <v>630</v>
+        <v>870</v>
       </c>
       <c r="S53" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T53" s="34" t="str">
-        <f>IF(ISBLANK(U53),SUBSTITUTE("18 %",".",","),IF(U53&lt;=554,SUBSTITUTE("5 %",".",","),IF(U53&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U53&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
+        <f>IF(ISBLANK(U53),SUBSTITUTE("18 %",".",","),IF(U53&lt;=766,SUBSTITUTE("5 %",".",","),IF(U53&lt;=783,SUBSTITUTE("5.7 %",".",","),IF(U53&lt;=809,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>5,7 %</v>
       </c>
       <c r="U53" s="50">
-        <v>567</v>
+        <v>783</v>
       </c>
       <c r="X53" s="48"/>
       <c r="Y53" s="48"/>
@@ -11814,68 +12012,68 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="33">
-        <v>135474384</v>
+        <v>135816614</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>230</v>
+        <v>284</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F54" s="34">
         <v>20</v>
       </c>
       <c r="G54" s="35">
-        <v>46120.033033692132</v>
+        <v>46127.124837905103</v>
       </c>
       <c r="H54" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="J54" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K54" s="38">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="L54" s="39" t="s">
-        <v>232</v>
+        <v>286</v>
       </c>
       <c r="M54" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N54" s="41">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="O54" s="42" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="P54" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q54" s="43">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="R54" s="44">
-        <v>630</v>
+        <v>870</v>
       </c>
       <c r="S54" s="34" t="s">
         <v>58</v>
       </c>
       <c r="T54" s="34" t="str">
-        <f>IF(ISBLANK(U54),SUBSTITUTE("18 %",".",","),IF(U54&lt;=554,SUBSTITUTE("5 %",".",","),IF(U54&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U54&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
+        <f>IF(ISBLANK(U54),SUBSTITUTE("18 %",".",","),IF(U54&lt;=530,SUBSTITUTE("5 %",".",","),IF(U54&lt;=546,SUBSTITUTE("5.7 %",".",","),IF(U54&lt;=564,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>5,7 %</v>
       </c>
       <c r="U54" s="50">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="X54" s="48"/>
       <c r="Y54" s="48"/>
@@ -11891,55 +12089,55 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="33">
-        <v>135463440</v>
+        <v>135812610</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F55" s="34">
         <v>20</v>
       </c>
       <c r="G55" s="35">
-        <v>46120.031321192131</v>
+        <v>46127.124277326388</v>
       </c>
       <c r="H55" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="J55" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K55" s="38">
-        <v>586</v>
+        <v>507</v>
       </c>
       <c r="L55" s="39" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="M55" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N55" s="41">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="O55" s="42" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="P55" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q55" s="43">
-        <v>554</v>
+        <v>456</v>
       </c>
       <c r="R55" s="44">
         <v>630</v>
@@ -11948,11 +12146,11 @@
         <v>58</v>
       </c>
       <c r="T55" s="34" t="str">
-        <f>IF(ISBLANK(U55),SUBSTITUTE("18 %",".",","),IF(U55&lt;=554,SUBSTITUTE("5 %",".",","),IF(U55&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U55&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
-      </c>
-      <c r="U55" s="50">
-        <v>567</v>
+        <f>IF(ISBLANK(U55),SUBSTITUTE("18 %",".",","),IF(U55&lt;=456,SUBSTITUTE("5 %",".",","),IF(U55&lt;=481,SUBSTITUTE("5.7 %",".",","),IF(U55&lt;=507,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U55" s="51">
+        <v>630</v>
       </c>
       <c r="X55" s="48"/>
       <c r="Y55" s="48"/>
@@ -11968,55 +12166,55 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="33">
-        <v>135461381</v>
+        <v>135810716</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="F56" s="34">
         <v>20</v>
       </c>
       <c r="G56" s="35">
-        <v>46120.031016516201</v>
+        <v>46127.124003032397</v>
       </c>
       <c r="H56" s="35">
-        <v>46126.999305555553</v>
+        <v>46133.999305555553</v>
       </c>
       <c r="I56" s="36" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="J56" s="36" t="s">
         <v>55</v>
       </c>
       <c r="K56" s="38">
-        <v>586</v>
+        <v>507</v>
       </c>
       <c r="L56" s="39" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="M56" s="39" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N56" s="41">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="O56" s="42" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="P56" s="42" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Q56" s="43">
-        <v>554</v>
+        <v>456</v>
       </c>
       <c r="R56" s="44">
         <v>630</v>
@@ -12025,11 +12223,11 @@
         <v>58</v>
       </c>
       <c r="T56" s="34" t="str">
-        <f>IF(ISBLANK(U56),SUBSTITUTE("18 %",".",","),IF(U56&lt;=554,SUBSTITUTE("5 %",".",","),IF(U56&lt;=567,SUBSTITUTE("6.4 %",".",","),IF(U56&lt;=586,SUBSTITUTE("7.1 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
-        <v>6,4 %</v>
-      </c>
-      <c r="U56" s="50">
-        <v>567</v>
+        <f>IF(ISBLANK(U56),SUBSTITUTE("18 %",".",","),IF(U56&lt;=456,SUBSTITUTE("5 %",".",","),IF(U56&lt;=481,SUBSTITUTE("5.7 %",".",","),IF(U56&lt;=507,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U56" s="51">
+        <v>630</v>
       </c>
       <c r="X56" s="48"/>
       <c r="Y56" s="48"/>
@@ -12044,23 +12242,70 @@
       <c r="AH56" s="48"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="E57" s="48"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="53"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="55"/>
-      <c r="L57" s="56"/>
-      <c r="M57" s="57"/>
-      <c r="N57" s="58"/>
-      <c r="O57" s="59"/>
-      <c r="P57" s="60"/>
-      <c r="Q57" s="61"/>
-      <c r="R57" s="62"/>
-      <c r="S57" s="52"/>
-      <c r="T57" s="48"/>
-      <c r="U57" s="63"/>
+      <c r="A57" s="33">
+        <v>135809212</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="F57" s="34">
+        <v>20</v>
+      </c>
+      <c r="G57" s="35">
+        <v>46127.123782465278</v>
+      </c>
+      <c r="H57" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I57" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="J57" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K57" s="38">
+        <v>507</v>
+      </c>
+      <c r="L57" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="M57" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N57" s="41">
+        <v>481</v>
+      </c>
+      <c r="O57" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="P57" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q57" s="43">
+        <v>456</v>
+      </c>
+      <c r="R57" s="44">
+        <v>630</v>
+      </c>
+      <c r="S57" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="T57" s="34" t="str">
+        <f>IF(ISBLANK(U57),SUBSTITUTE("18 %",".",","),IF(U57&lt;=456,SUBSTITUTE("5 %",".",","),IF(U57&lt;=481,SUBSTITUTE("5.7 %",".",","),IF(U57&lt;=507,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U57" s="51">
+        <v>630</v>
+      </c>
       <c r="X57" s="48"/>
       <c r="Y57" s="48"/>
       <c r="Z57" s="48"/>
@@ -12074,23 +12319,70 @@
       <c r="AH57" s="48"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="E58" s="48"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="55"/>
-      <c r="L58" s="56"/>
-      <c r="M58" s="57"/>
-      <c r="N58" s="58"/>
-      <c r="O58" s="59"/>
-      <c r="P58" s="60"/>
-      <c r="Q58" s="61"/>
-      <c r="R58" s="62"/>
-      <c r="S58" s="52"/>
-      <c r="T58" s="48"/>
-      <c r="U58" s="63"/>
+      <c r="A58" s="33">
+        <v>135804154</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="F58" s="34">
+        <v>20</v>
+      </c>
+      <c r="G58" s="35">
+        <v>46127.123031157411</v>
+      </c>
+      <c r="H58" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I58" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="J58" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K58" s="38">
+        <v>427</v>
+      </c>
+      <c r="L58" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="M58" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N58" s="41">
+        <v>413</v>
+      </c>
+      <c r="O58" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="P58" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q58" s="43">
+        <v>400</v>
+      </c>
+      <c r="R58" s="44">
+        <v>630</v>
+      </c>
+      <c r="S58" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="T58" s="34" t="str">
+        <f>IF(ISBLANK(U58),SUBSTITUTE("18 %",".",","),IF(U58&lt;=400,SUBSTITUTE("5 %",".",","),IF(U58&lt;=413,SUBSTITUTE("5.7 %",".",","),IF(U58&lt;=427,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U58" s="51">
+        <v>630</v>
+      </c>
       <c r="X58" s="48"/>
       <c r="Y58" s="48"/>
       <c r="Z58" s="48"/>
@@ -12104,23 +12396,70 @@
       <c r="AH58" s="48"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="E59" s="48"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="53"/>
-      <c r="J59" s="54"/>
-      <c r="K59" s="55"/>
-      <c r="L59" s="56"/>
-      <c r="M59" s="57"/>
-      <c r="N59" s="58"/>
-      <c r="O59" s="59"/>
-      <c r="P59" s="60"/>
-      <c r="Q59" s="61"/>
-      <c r="R59" s="62"/>
-      <c r="S59" s="52"/>
-      <c r="T59" s="48"/>
-      <c r="U59" s="63"/>
+      <c r="A59" s="33">
+        <v>135784843</v>
+      </c>
+      <c r="B59" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="F59" s="34">
+        <v>20</v>
+      </c>
+      <c r="G59" s="35">
+        <v>46127.120340555557</v>
+      </c>
+      <c r="H59" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I59" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="J59" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K59" s="38">
+        <v>433</v>
+      </c>
+      <c r="L59" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="M59" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N59" s="41">
+        <v>419</v>
+      </c>
+      <c r="O59" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="P59" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q59" s="43">
+        <v>405</v>
+      </c>
+      <c r="R59" s="44">
+        <v>630</v>
+      </c>
+      <c r="S59" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="T59" s="34" t="str">
+        <f>IF(ISBLANK(U59),SUBSTITUTE("18 %",".",","),IF(U59&lt;=405,SUBSTITUTE("5 %",".",","),IF(U59&lt;=419,SUBSTITUTE("5.7 %",".",","),IF(U59&lt;=433,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U59" s="51">
+        <v>630</v>
+      </c>
       <c r="X59" s="48"/>
       <c r="Y59" s="48"/>
       <c r="Z59" s="48"/>
@@ -12134,23 +12473,70 @@
       <c r="AH59" s="48"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="E60" s="48"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="53"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="55"/>
-      <c r="L60" s="56"/>
-      <c r="M60" s="57"/>
-      <c r="N60" s="58"/>
-      <c r="O60" s="59"/>
-      <c r="P60" s="60"/>
-      <c r="Q60" s="61"/>
-      <c r="R60" s="62"/>
-      <c r="S60" s="52"/>
-      <c r="T60" s="48"/>
-      <c r="U60" s="63"/>
+      <c r="A60" s="33">
+        <v>135784690</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="F60" s="34">
+        <v>20</v>
+      </c>
+      <c r="G60" s="35">
+        <v>46127.120319016212</v>
+      </c>
+      <c r="H60" s="35">
+        <v>46133.999305555553</v>
+      </c>
+      <c r="I60" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="J60" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K60" s="38">
+        <v>507</v>
+      </c>
+      <c r="L60" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="M60" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N60" s="41">
+        <v>481</v>
+      </c>
+      <c r="O60" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="P60" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q60" s="43">
+        <v>456</v>
+      </c>
+      <c r="R60" s="44">
+        <v>630</v>
+      </c>
+      <c r="S60" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="T60" s="34" t="str">
+        <f>IF(ISBLANK(U60),SUBSTITUTE("18 %",".",","),IF(U60&lt;=456,SUBSTITUTE("5 %",".",","),IF(U60&lt;=481,SUBSTITUTE("5.7 %",".",","),IF(U60&lt;=507,SUBSTITUTE("6.4 %",".",","),SUBSTITUTE("18 %",".",",")))))</f>
+        <v>18 %</v>
+      </c>
+      <c r="U60" s="51">
+        <v>630</v>
+      </c>
       <c r="X60" s="48"/>
       <c r="Y60" s="48"/>
       <c r="Z60" s="48"/>
@@ -27160,6 +27546,10 @@
     <hyperlink ref="B54" r:id="rId53"/>
     <hyperlink ref="B55" r:id="rId54"/>
     <hyperlink ref="B56" r:id="rId55"/>
+    <hyperlink ref="B57" r:id="rId56"/>
+    <hyperlink ref="B58" r:id="rId57"/>
+    <hyperlink ref="B59" r:id="rId58"/>
+    <hyperlink ref="B60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
